--- a/GUA_Sube_Dokum.xlsx
+++ b/GUA_Sube_Dokum.xlsx
@@ -6,8 +6,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Şube Özeti" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Özet" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detaylı Döküm" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mağusa Şube" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intech Salamis Kiosk" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Şubesiz (Bekleyen)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -16,10 +19,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd.mm.yyyy"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="dd.mm.yyyy"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Aptos Narrow"/>
       <charset val="162"/>
@@ -39,12 +44,8 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
-    <font>
-      <b val="1"/>
-      <sz val="12"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -66,6 +67,11 @@
         <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -82,25 +88,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -498,936 +507,201 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>GUA COFFEE COMPANY TRADING LTD (AL000151) – Şube Bazlı Özet</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="45" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Şube bilgisi yalnızca fatura/irsaliye üzerinde yazan kayıtlar için doldurulmuştur; diğerleri boş bırakılmıştır. Detaylı Döküm sayfasındaki N sütunundan şube seçtikçe bu tablo otomatik güncellenir.</t>
+          <t>GUA COFFEE COMPANY TRADING LTD (AL000151) – Şube Özeti</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Şube</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Fatura Adedi</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Fatura Tutarı</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>İade</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Net Tutar</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Pay %</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Şube</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Fatura Adedi</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Fatura Tutarı (Borç)</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>İade Tutarı (Alacak)</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Net Tutar</t>
-        </is>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Mağusa Şube</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>8925</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1">
+        <f>C4-D4</f>
+        <v/>
+      </c>
+      <c r="F4" s="5">
+        <f>E4/E$7</f>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mağusa Şube</t>
-        </is>
-      </c>
-      <c r="B5">
-        <f>COUNTIFS('Detaylı Döküm'!$N$7:$N$150,A5,'Detaylı Döküm'!$E$7:$E$150,"&gt;0")</f>
-        <v/>
-      </c>
-      <c r="C5" s="1">
-        <f>SUMIFS('Detaylı Döküm'!$E$7:$E$150,'Detaylı Döküm'!$N$7:$N$150,A5)</f>
-        <v/>
-      </c>
-      <c r="D5" s="1">
-        <f>SUMIFS('Detaylı Döküm'!$F$7:$F$150,'Detaylı Döküm'!$N$7:$N$150,A5,'Detaylı Döküm'!$C$7:$C$150,"IADE FATURANIZ")</f>
-        <v/>
+          <t>Intech Salamis Kiosk</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="E5" s="1">
         <f>C5-D5</f>
         <v/>
       </c>
+      <c r="F5" s="5">
+        <f>E5/E$7</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Intech Salamis Kiosk</t>
-        </is>
-      </c>
-      <c r="B6">
-        <f>COUNTIFS('Detaylı Döküm'!$N$7:$N$150,A6,'Detaylı Döküm'!$E$7:$E$150,"&gt;0")</f>
-        <v/>
-      </c>
-      <c r="C6" s="1">
-        <f>SUMIFS('Detaylı Döküm'!$E$7:$E$150,'Detaylı Döküm'!$N$7:$N$150,A6)</f>
-        <v/>
-      </c>
-      <c r="D6" s="1">
-        <f>SUMIFS('Detaylı Döküm'!$F$7:$F$150,'Detaylı Döküm'!$N$7:$N$150,A6,'Detaylı Döküm'!$C$7:$C$150,"IADE FATURANIZ")</f>
-        <v/>
+          <t>Şubesi belirsiz</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>31</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>227767.11</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>13456.09</v>
       </c>
       <c r="E6" s="1">
         <f>C6-D6</f>
         <v/>
       </c>
+      <c r="F6" s="5">
+        <f>E6/E$7</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Şube belirtilmemiş (boş)</t>
-        </is>
-      </c>
-      <c r="B7">
-        <f>SUMPRODUCT(('Detaylı Döküm'!$N$7:$N$150="")*('Detaylı Döküm'!$C$7:$C$150="FATURAMIZ"))</f>
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>FATURA TOPLAMI</t>
+        </is>
+      </c>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
         <v/>
       </c>
-      <c r="C7" s="1">
-        <f>SUMIFS('Detaylı Döküm'!$E$7:$E$150,'Detaylı Döküm'!$C$7:$C$150,"FATURAMIZ",'Detaylı Döküm'!$N$7:$N$150,"")</f>
+      <c r="C7" s="7">
+        <f>SUM(C4:C6)</f>
         <v/>
       </c>
-      <c r="D7" s="1">
-        <f>SUMIFS('Detaylı Döküm'!$F$7:$F$150,'Detaylı Döküm'!$C$7:$C$150,"IADE FATURANIZ",'Detaylı Döküm'!$N$7:$N$150,"")</f>
+      <c r="D7" s="7">
+        <f>SUM(D4:D6)</f>
         <v/>
       </c>
-      <c r="E7" s="1">
-        <f>C7-D7</f>
+      <c r="E7" s="7">
+        <f>SUM(E4:E6)</f>
         <v/>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>TOPLAM</t>
-        </is>
-      </c>
-      <c r="B8" s="6">
-        <f>SUM(B5:B7)</f>
+      <c r="F7" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Ödemeler (şubesiz, genel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Devreden bakiye (2026 öncesi)</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>43927.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>13.04.2026 – GD/282/HAVALE</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>-113526.11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>28.08.2026 – GD/567/ İŞBANKASI HAVALE</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>-97623.25</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Cari borç bakiyesi (dökümle aynı)</t>
+        </is>
+      </c>
+      <c r="E13" s="10">
+        <f>E7+SUM(E10:E12)</f>
         <v/>
       </c>
-      <c r="C8" s="7">
-        <f>SUM(C5:C7)</f>
-        <v/>
-      </c>
-      <c r="D8" s="7">
-        <f>SUM(D5:D7)</f>
-        <v/>
-      </c>
-      <c r="E8" s="7">
-        <f>SUM(E5:E7)</f>
-        <v/>
-      </c>
-      <c r="F8" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Fatura Listesi</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Tarih</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Fiş No</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Tür</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Tutar</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Şube</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10">
-        <f>'Detaylı Döküm'!A7</f>
-        <v/>
-      </c>
-      <c r="B13">
-        <f>'Detaylı Döküm'!B7</f>
-        <v/>
-      </c>
-      <c r="C13">
-        <f>'Detaylı Döküm'!C7</f>
-        <v/>
-      </c>
-      <c r="D13" s="1">
-        <f>IF('Detaylı Döküm'!E7&gt;0,'Detaylı Döküm'!E7,-'Detaylı Döküm'!F7)</f>
-        <v/>
-      </c>
-      <c r="E13">
-        <f>IF('Detaylı Döküm'!N7="","",'Detaylı Döküm'!N7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10">
-        <f>'Detaylı Döküm'!A11</f>
-        <v/>
-      </c>
-      <c r="B14">
-        <f>'Detaylı Döküm'!B11</f>
-        <v/>
-      </c>
-      <c r="C14">
-        <f>'Detaylı Döküm'!C11</f>
-        <v/>
-      </c>
-      <c r="D14" s="1">
-        <f>IF('Detaylı Döküm'!E11&gt;0,'Detaylı Döküm'!E11,-'Detaylı Döküm'!F11)</f>
-        <v/>
-      </c>
-      <c r="E14">
-        <f>IF('Detaylı Döküm'!N11="","",'Detaylı Döküm'!N11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10">
-        <f>'Detaylı Döküm'!A14</f>
-        <v/>
-      </c>
-      <c r="B15">
-        <f>'Detaylı Döküm'!B14</f>
-        <v/>
-      </c>
-      <c r="C15">
-        <f>'Detaylı Döküm'!C14</f>
-        <v/>
-      </c>
-      <c r="D15" s="1">
-        <f>IF('Detaylı Döküm'!E14&gt;0,'Detaylı Döküm'!E14,-'Detaylı Döküm'!F14)</f>
-        <v/>
-      </c>
-      <c r="E15">
-        <f>IF('Detaylı Döküm'!N14="","",'Detaylı Döküm'!N14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10">
-        <f>'Detaylı Döküm'!A17</f>
-        <v/>
-      </c>
-      <c r="B16">
-        <f>'Detaylı Döküm'!B17</f>
-        <v/>
-      </c>
-      <c r="C16">
-        <f>'Detaylı Döküm'!C17</f>
-        <v/>
-      </c>
-      <c r="D16" s="1">
-        <f>IF('Detaylı Döküm'!E17&gt;0,'Detaylı Döküm'!E17,-'Detaylı Döküm'!F17)</f>
-        <v/>
-      </c>
-      <c r="E16">
-        <f>IF('Detaylı Döküm'!N17="","",'Detaylı Döküm'!N17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10">
-        <f>'Detaylı Döküm'!A20</f>
-        <v/>
-      </c>
-      <c r="B17">
-        <f>'Detaylı Döküm'!B20</f>
-        <v/>
-      </c>
-      <c r="C17">
-        <f>'Detaylı Döküm'!C20</f>
-        <v/>
-      </c>
-      <c r="D17" s="1">
-        <f>IF('Detaylı Döküm'!E20&gt;0,'Detaylı Döküm'!E20,-'Detaylı Döküm'!F20)</f>
-        <v/>
-      </c>
-      <c r="E17">
-        <f>IF('Detaylı Döküm'!N20="","",'Detaylı Döküm'!N20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10">
-        <f>'Detaylı Döküm'!A23</f>
-        <v/>
-      </c>
-      <c r="B18">
-        <f>'Detaylı Döküm'!B23</f>
-        <v/>
-      </c>
-      <c r="C18">
-        <f>'Detaylı Döküm'!C23</f>
-        <v/>
-      </c>
-      <c r="D18" s="1">
-        <f>IF('Detaylı Döküm'!E23&gt;0,'Detaylı Döküm'!E23,-'Detaylı Döküm'!F23)</f>
-        <v/>
-      </c>
-      <c r="E18">
-        <f>IF('Detaylı Döküm'!N23="","",'Detaylı Döküm'!N23)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10">
-        <f>'Detaylı Döküm'!A27</f>
-        <v/>
-      </c>
-      <c r="B19">
-        <f>'Detaylı Döküm'!B27</f>
-        <v/>
-      </c>
-      <c r="C19">
-        <f>'Detaylı Döküm'!C27</f>
-        <v/>
-      </c>
-      <c r="D19" s="1">
-        <f>IF('Detaylı Döküm'!E27&gt;0,'Detaylı Döküm'!E27,-'Detaylı Döküm'!F27)</f>
-        <v/>
-      </c>
-      <c r="E19">
-        <f>IF('Detaylı Döküm'!N27="","",'Detaylı Döküm'!N27)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10">
-        <f>'Detaylı Döküm'!A30</f>
-        <v/>
-      </c>
-      <c r="B20">
-        <f>'Detaylı Döküm'!B30</f>
-        <v/>
-      </c>
-      <c r="C20">
-        <f>'Detaylı Döküm'!C30</f>
-        <v/>
-      </c>
-      <c r="D20" s="1">
-        <f>IF('Detaylı Döküm'!E30&gt;0,'Detaylı Döküm'!E30,-'Detaylı Döküm'!F30)</f>
-        <v/>
-      </c>
-      <c r="E20">
-        <f>IF('Detaylı Döküm'!N30="","",'Detaylı Döküm'!N30)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10">
-        <f>'Detaylı Döküm'!A35</f>
-        <v/>
-      </c>
-      <c r="B21">
-        <f>'Detaylı Döküm'!B35</f>
-        <v/>
-      </c>
-      <c r="C21">
-        <f>'Detaylı Döküm'!C35</f>
-        <v/>
-      </c>
-      <c r="D21" s="1">
-        <f>IF('Detaylı Döküm'!E35&gt;0,'Detaylı Döküm'!E35,-'Detaylı Döküm'!F35)</f>
-        <v/>
-      </c>
-      <c r="E21">
-        <f>IF('Detaylı Döküm'!N35="","",'Detaylı Döküm'!N35)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10">
-        <f>'Detaylı Döküm'!A39</f>
-        <v/>
-      </c>
-      <c r="B22">
-        <f>'Detaylı Döküm'!B39</f>
-        <v/>
-      </c>
-      <c r="C22">
-        <f>'Detaylı Döküm'!C39</f>
-        <v/>
-      </c>
-      <c r="D22" s="1">
-        <f>IF('Detaylı Döküm'!E39&gt;0,'Detaylı Döküm'!E39,-'Detaylı Döküm'!F39)</f>
-        <v/>
-      </c>
-      <c r="E22">
-        <f>IF('Detaylı Döküm'!N39="","",'Detaylı Döküm'!N39)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10">
-        <f>'Detaylı Döküm'!A42</f>
-        <v/>
-      </c>
-      <c r="B23">
-        <f>'Detaylı Döküm'!B42</f>
-        <v/>
-      </c>
-      <c r="C23">
-        <f>'Detaylı Döküm'!C42</f>
-        <v/>
-      </c>
-      <c r="D23" s="1">
-        <f>IF('Detaylı Döküm'!E42&gt;0,'Detaylı Döküm'!E42,-'Detaylı Döküm'!F42)</f>
-        <v/>
-      </c>
-      <c r="E23">
-        <f>IF('Detaylı Döküm'!N42="","",'Detaylı Döküm'!N42)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10">
-        <f>'Detaylı Döküm'!A45</f>
-        <v/>
-      </c>
-      <c r="B24">
-        <f>'Detaylı Döküm'!B45</f>
-        <v/>
-      </c>
-      <c r="C24">
-        <f>'Detaylı Döküm'!C45</f>
-        <v/>
-      </c>
-      <c r="D24" s="1">
-        <f>IF('Detaylı Döküm'!E45&gt;0,'Detaylı Döküm'!E45,-'Detaylı Döküm'!F45)</f>
-        <v/>
-      </c>
-      <c r="E24">
-        <f>IF('Detaylı Döküm'!N45="","",'Detaylı Döküm'!N45)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10">
-        <f>'Detaylı Döküm'!A51</f>
-        <v/>
-      </c>
-      <c r="B25">
-        <f>'Detaylı Döküm'!B51</f>
-        <v/>
-      </c>
-      <c r="C25">
-        <f>'Detaylı Döküm'!C51</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>IF('Detaylı Döküm'!E51&gt;0,'Detaylı Döküm'!E51,-'Detaylı Döküm'!F51)</f>
-        <v/>
-      </c>
-      <c r="E25">
-        <f>IF('Detaylı Döküm'!N51="","",'Detaylı Döküm'!N51)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10">
-        <f>'Detaylı Döküm'!A57</f>
-        <v/>
-      </c>
-      <c r="B26">
-        <f>'Detaylı Döküm'!B57</f>
-        <v/>
-      </c>
-      <c r="C26">
-        <f>'Detaylı Döküm'!C57</f>
-        <v/>
-      </c>
-      <c r="D26" s="1">
-        <f>IF('Detaylı Döküm'!E57&gt;0,'Detaylı Döküm'!E57,-'Detaylı Döküm'!F57)</f>
-        <v/>
-      </c>
-      <c r="E26">
-        <f>IF('Detaylı Döküm'!N57="","",'Detaylı Döküm'!N57)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="10">
-        <f>'Detaylı Döküm'!A60</f>
-        <v/>
-      </c>
-      <c r="B27">
-        <f>'Detaylı Döküm'!B60</f>
-        <v/>
-      </c>
-      <c r="C27">
-        <f>'Detaylı Döküm'!C60</f>
-        <v/>
-      </c>
-      <c r="D27" s="1">
-        <f>IF('Detaylı Döküm'!E60&gt;0,'Detaylı Döküm'!E60,-'Detaylı Döküm'!F60)</f>
-        <v/>
-      </c>
-      <c r="E27">
-        <f>IF('Detaylı Döküm'!N60="","",'Detaylı Döküm'!N60)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="10">
-        <f>'Detaylı Döküm'!A63</f>
-        <v/>
-      </c>
-      <c r="B28">
-        <f>'Detaylı Döküm'!B63</f>
-        <v/>
-      </c>
-      <c r="C28">
-        <f>'Detaylı Döküm'!C63</f>
-        <v/>
-      </c>
-      <c r="D28" s="1">
-        <f>IF('Detaylı Döküm'!E63&gt;0,'Detaylı Döküm'!E63,-'Detaylı Döküm'!F63)</f>
-        <v/>
-      </c>
-      <c r="E28">
-        <f>IF('Detaylı Döküm'!N63="","",'Detaylı Döküm'!N63)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="10">
-        <f>'Detaylı Döküm'!A70</f>
-        <v/>
-      </c>
-      <c r="B29">
-        <f>'Detaylı Döküm'!B70</f>
-        <v/>
-      </c>
-      <c r="C29">
-        <f>'Detaylı Döküm'!C70</f>
-        <v/>
-      </c>
-      <c r="D29" s="1">
-        <f>IF('Detaylı Döküm'!E70&gt;0,'Detaylı Döküm'!E70,-'Detaylı Döküm'!F70)</f>
-        <v/>
-      </c>
-      <c r="E29">
-        <f>IF('Detaylı Döküm'!N70="","",'Detaylı Döküm'!N70)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10">
-        <f>'Detaylı Döküm'!A74</f>
-        <v/>
-      </c>
-      <c r="B30">
-        <f>'Detaylı Döküm'!B74</f>
-        <v/>
-      </c>
-      <c r="C30">
-        <f>'Detaylı Döküm'!C74</f>
-        <v/>
-      </c>
-      <c r="D30" s="1">
-        <f>IF('Detaylı Döküm'!E74&gt;0,'Detaylı Döküm'!E74,-'Detaylı Döküm'!F74)</f>
-        <v/>
-      </c>
-      <c r="E30">
-        <f>IF('Detaylı Döküm'!N74="","",'Detaylı Döküm'!N74)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10">
-        <f>'Detaylı Döküm'!A77</f>
-        <v/>
-      </c>
-      <c r="B31">
-        <f>'Detaylı Döküm'!B77</f>
-        <v/>
-      </c>
-      <c r="C31">
-        <f>'Detaylı Döküm'!C77</f>
-        <v/>
-      </c>
-      <c r="D31" s="1">
-        <f>IF('Detaylı Döküm'!E77&gt;0,'Detaylı Döküm'!E77,-'Detaylı Döküm'!F77)</f>
-        <v/>
-      </c>
-      <c r="E31">
-        <f>IF('Detaylı Döküm'!N77="","",'Detaylı Döküm'!N77)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10">
-        <f>'Detaylı Döküm'!A84</f>
-        <v/>
-      </c>
-      <c r="B32">
-        <f>'Detaylı Döküm'!B84</f>
-        <v/>
-      </c>
-      <c r="C32">
-        <f>'Detaylı Döküm'!C84</f>
-        <v/>
-      </c>
-      <c r="D32" s="1">
-        <f>IF('Detaylı Döküm'!E84&gt;0,'Detaylı Döküm'!E84,-'Detaylı Döküm'!F84)</f>
-        <v/>
-      </c>
-      <c r="E32">
-        <f>IF('Detaylı Döküm'!N84="","",'Detaylı Döküm'!N84)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="10">
-        <f>'Detaylı Döküm'!A87</f>
-        <v/>
-      </c>
-      <c r="B33">
-        <f>'Detaylı Döküm'!B87</f>
-        <v/>
-      </c>
-      <c r="C33">
-        <f>'Detaylı Döküm'!C87</f>
-        <v/>
-      </c>
-      <c r="D33" s="1">
-        <f>IF('Detaylı Döküm'!E87&gt;0,'Detaylı Döküm'!E87,-'Detaylı Döküm'!F87)</f>
-        <v/>
-      </c>
-      <c r="E33">
-        <f>IF('Detaylı Döküm'!N87="","",'Detaylı Döküm'!N87)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="10">
-        <f>'Detaylı Döküm'!A94</f>
-        <v/>
-      </c>
-      <c r="B34">
-        <f>'Detaylı Döküm'!B94</f>
-        <v/>
-      </c>
-      <c r="C34">
-        <f>'Detaylı Döküm'!C94</f>
-        <v/>
-      </c>
-      <c r="D34" s="1">
-        <f>IF('Detaylı Döküm'!E94&gt;0,'Detaylı Döküm'!E94,-'Detaylı Döküm'!F94)</f>
-        <v/>
-      </c>
-      <c r="E34">
-        <f>IF('Detaylı Döküm'!N94="","",'Detaylı Döküm'!N94)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="10">
-        <f>'Detaylı Döküm'!A97</f>
-        <v/>
-      </c>
-      <c r="B35">
-        <f>'Detaylı Döküm'!B97</f>
-        <v/>
-      </c>
-      <c r="C35">
-        <f>'Detaylı Döküm'!C97</f>
-        <v/>
-      </c>
-      <c r="D35" s="1">
-        <f>IF('Detaylı Döküm'!E97&gt;0,'Detaylı Döküm'!E97,-'Detaylı Döküm'!F97)</f>
-        <v/>
-      </c>
-      <c r="E35">
-        <f>IF('Detaylı Döküm'!N97="","",'Detaylı Döküm'!N97)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="10">
-        <f>'Detaylı Döküm'!A100</f>
-        <v/>
-      </c>
-      <c r="B36">
-        <f>'Detaylı Döküm'!B100</f>
-        <v/>
-      </c>
-      <c r="C36">
-        <f>'Detaylı Döküm'!C100</f>
-        <v/>
-      </c>
-      <c r="D36" s="1">
-        <f>IF('Detaylı Döküm'!E100&gt;0,'Detaylı Döküm'!E100,-'Detaylı Döküm'!F100)</f>
-        <v/>
-      </c>
-      <c r="E36">
-        <f>IF('Detaylı Döküm'!N100="","",'Detaylı Döküm'!N100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="10">
-        <f>'Detaylı Döküm'!A107</f>
-        <v/>
-      </c>
-      <c r="B37">
-        <f>'Detaylı Döküm'!B107</f>
-        <v/>
-      </c>
-      <c r="C37">
-        <f>'Detaylı Döküm'!C107</f>
-        <v/>
-      </c>
-      <c r="D37" s="1">
-        <f>IF('Detaylı Döküm'!E107&gt;0,'Detaylı Döküm'!E107,-'Detaylı Döküm'!F107)</f>
-        <v/>
-      </c>
-      <c r="E37">
-        <f>IF('Detaylı Döküm'!N107="","",'Detaylı Döküm'!N107)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="10">
-        <f>'Detaylı Döküm'!A110</f>
-        <v/>
-      </c>
-      <c r="B38">
-        <f>'Detaylı Döküm'!B110</f>
-        <v/>
-      </c>
-      <c r="C38">
-        <f>'Detaylı Döküm'!C110</f>
-        <v/>
-      </c>
-      <c r="D38" s="1">
-        <f>IF('Detaylı Döküm'!E110&gt;0,'Detaylı Döküm'!E110,-'Detaylı Döküm'!F110)</f>
-        <v/>
-      </c>
-      <c r="E38">
-        <f>IF('Detaylı Döküm'!N110="","",'Detaylı Döküm'!N110)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="10">
-        <f>'Detaylı Döküm'!A113</f>
-        <v/>
-      </c>
-      <c r="B39">
-        <f>'Detaylı Döküm'!B113</f>
-        <v/>
-      </c>
-      <c r="C39">
-        <f>'Detaylı Döküm'!C113</f>
-        <v/>
-      </c>
-      <c r="D39" s="1">
-        <f>IF('Detaylı Döküm'!E113&gt;0,'Detaylı Döküm'!E113,-'Detaylı Döküm'!F113)</f>
-        <v/>
-      </c>
-      <c r="E39">
-        <f>IF('Detaylı Döküm'!N113="","",'Detaylı Döküm'!N113)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="10">
-        <f>'Detaylı Döküm'!A117</f>
-        <v/>
-      </c>
-      <c r="B40">
-        <f>'Detaylı Döküm'!B117</f>
-        <v/>
-      </c>
-      <c r="C40">
-        <f>'Detaylı Döküm'!C117</f>
-        <v/>
-      </c>
-      <c r="D40" s="1">
-        <f>IF('Detaylı Döküm'!E117&gt;0,'Detaylı Döküm'!E117,-'Detaylı Döküm'!F117)</f>
-        <v/>
-      </c>
-      <c r="E40">
-        <f>IF('Detaylı Döküm'!N117="","",'Detaylı Döküm'!N117)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="10">
-        <f>'Detaylı Döküm'!A121</f>
-        <v/>
-      </c>
-      <c r="B41">
-        <f>'Detaylı Döküm'!B121</f>
-        <v/>
-      </c>
-      <c r="C41">
-        <f>'Detaylı Döküm'!C121</f>
-        <v/>
-      </c>
-      <c r="D41" s="1">
-        <f>IF('Detaylı Döküm'!E121&gt;0,'Detaylı Döküm'!E121,-'Detaylı Döküm'!F121)</f>
-        <v/>
-      </c>
-      <c r="E41">
-        <f>IF('Detaylı Döküm'!N121="","",'Detaylı Döküm'!N121)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="10">
-        <f>'Detaylı Döküm'!A128</f>
-        <v/>
-      </c>
-      <c r="B42">
-        <f>'Detaylı Döküm'!B128</f>
-        <v/>
-      </c>
-      <c r="C42">
-        <f>'Detaylı Döküm'!C128</f>
-        <v/>
-      </c>
-      <c r="D42" s="1">
-        <f>IF('Detaylı Döküm'!E128&gt;0,'Detaylı Döküm'!E128,-'Detaylı Döküm'!F128)</f>
-        <v/>
-      </c>
-      <c r="E42">
-        <f>IF('Detaylı Döküm'!N128="","",'Detaylı Döküm'!N128)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="10">
-        <f>'Detaylı Döküm'!A131</f>
-        <v/>
-      </c>
-      <c r="B43">
-        <f>'Detaylı Döküm'!B131</f>
-        <v/>
-      </c>
-      <c r="C43">
-        <f>'Detaylı Döküm'!C131</f>
-        <v/>
-      </c>
-      <c r="D43" s="1">
-        <f>IF('Detaylı Döküm'!E131&gt;0,'Detaylı Döküm'!E131,-'Detaylı Döküm'!F131)</f>
-        <v/>
-      </c>
-      <c r="E43">
-        <f>IF('Detaylı Döküm'!N131="","",'Detaylı Döküm'!N131)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="10">
-        <f>'Detaylı Döküm'!A137</f>
-        <v/>
-      </c>
-      <c r="B44">
-        <f>'Detaylı Döküm'!B137</f>
-        <v/>
-      </c>
-      <c r="C44">
-        <f>'Detaylı Döküm'!C137</f>
-        <v/>
-      </c>
-      <c r="D44" s="1">
-        <f>IF('Detaylı Döküm'!E137&gt;0,'Detaylı Döküm'!E137,-'Detaylı Döküm'!F137)</f>
-        <v/>
-      </c>
-      <c r="E44">
-        <f>IF('Detaylı Döküm'!N137="","",'Detaylı Döküm'!N137)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="10">
-        <f>'Detaylı Döküm'!A144</f>
-        <v/>
-      </c>
-      <c r="B45">
-        <f>'Detaylı Döküm'!B144</f>
-        <v/>
-      </c>
-      <c r="C45">
-        <f>'Detaylı Döküm'!C144</f>
-        <v/>
-      </c>
-      <c r="D45" s="1">
-        <f>IF('Detaylı Döküm'!E144&gt;0,'Detaylı Döküm'!E144,-'Detaylı Döküm'!F144)</f>
-        <v/>
-      </c>
-      <c r="E45">
-        <f>IF('Detaylı Döküm'!N144="","",'Detaylı Döküm'!N144)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="10">
-        <f>'Detaylı Döküm'!A148</f>
-        <v/>
-      </c>
-      <c r="B46">
-        <f>'Detaylı Döküm'!B148</f>
-        <v/>
-      </c>
-      <c r="C46">
-        <f>'Detaylı Döküm'!C148</f>
-        <v/>
-      </c>
-      <c r="D46" s="1">
-        <f>IF('Detaylı Döküm'!E148&gt;0,'Detaylı Döküm'!E148,-'Detaylı Döküm'!F148)</f>
-        <v/>
-      </c>
-      <c r="E46">
-        <f>IF('Detaylı Döküm'!N148="","",'Detaylı Döküm'!N148)</f>
-        <v/>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:F2"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1530,7 +804,7 @@
           <t>Plasiyer Kodu</t>
         </is>
       </c>
-      <c r="N5" s="11" t="inlineStr">
+      <c r="N5" s="9" t="inlineStr">
         <is>
           <t>Şube</t>
         </is>
@@ -1589,7 +863,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N7" s="12" t="n"/>
+      <c r="N7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -1779,7 +1053,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N11" s="12" t="n"/>
+      <c r="N11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -1923,7 +1197,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N14" s="12" t="n"/>
+      <c r="N14" s="11" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
@@ -2067,7 +1341,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N17" s="12" t="n"/>
+      <c r="N17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
@@ -2211,7 +1485,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N20" s="12" t="n"/>
+      <c r="N20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
@@ -2355,7 +1629,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N23" s="12" t="n"/>
+      <c r="N23" s="11" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
@@ -2545,7 +1819,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N27" s="12" t="n"/>
+      <c r="N27" s="11" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
@@ -2689,7 +1963,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N30" s="12" t="n"/>
+      <c r="N30" s="11" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
@@ -2925,7 +2199,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N35" s="12" t="n"/>
+      <c r="N35" s="11" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="B36" t="inlineStr">
@@ -3115,7 +2389,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N39" s="12" t="n"/>
+      <c r="N39" s="11" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="B40" t="inlineStr">
@@ -3259,7 +2533,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N42" s="12" t="n"/>
+      <c r="N42" s="11" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="B43" t="inlineStr">
@@ -3403,7 +2677,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N45" s="12" t="n"/>
+      <c r="N45" s="11" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="B46" t="inlineStr">
@@ -3674,7 +2948,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N51" s="12" t="n"/>
+      <c r="N51" s="11" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="B52" t="inlineStr">
@@ -3956,7 +3230,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N57" s="12" t="n"/>
+      <c r="N57" s="11" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="B58" t="inlineStr">
@@ -4100,7 +3374,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N60" s="12" t="n"/>
+      <c r="N60" s="11" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="B61" t="inlineStr">
@@ -4244,7 +3518,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N63" s="12" t="n"/>
+      <c r="N63" s="11" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="B64" t="inlineStr">
@@ -4572,7 +3846,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N70" s="12" t="n"/>
+      <c r="N70" s="11" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="B71" t="inlineStr">
@@ -4762,7 +4036,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N74" s="12" t="n"/>
+      <c r="N74" s="11" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="B75" t="inlineStr">
@@ -4906,7 +4180,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N77" s="12" t="n"/>
+      <c r="N77" s="11" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="B78" t="inlineStr">
@@ -5234,7 +4508,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N84" s="12" t="n"/>
+      <c r="N84" s="11" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="B85" t="inlineStr">
@@ -5378,7 +4652,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N87" s="12" t="n"/>
+      <c r="N87" s="11" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="B88" t="inlineStr">
@@ -5706,7 +4980,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N94" s="12" t="n"/>
+      <c r="N94" s="11" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="B95" t="inlineStr">
@@ -5850,7 +5124,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N97" s="12" t="n"/>
+      <c r="N97" s="11" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="B98" t="inlineStr">
@@ -5994,7 +5268,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N100" s="12" t="n"/>
+      <c r="N100" s="11" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="B101" t="inlineStr">
@@ -6322,7 +5596,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N107" s="12" t="n"/>
+      <c r="N107" s="11" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="B108" t="inlineStr">
@@ -6466,7 +5740,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N110" s="12" t="n"/>
+      <c r="N110" s="11" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="B111" t="inlineStr">
@@ -6610,7 +5884,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N113" s="12" t="n"/>
+      <c r="N113" s="11" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="B114" t="inlineStr">
@@ -6800,7 +6074,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N117" s="12" t="n"/>
+      <c r="N117" s="11" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="B118" t="inlineStr">
@@ -6990,7 +6264,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N121" s="12" t="n"/>
+      <c r="N121" s="11" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="B122" t="inlineStr">
@@ -7307,7 +6581,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N128" s="12" t="n"/>
+      <c r="N128" s="11" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="B129" t="inlineStr">
@@ -7451,7 +6725,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N131" s="12" t="n"/>
+      <c r="N131" s="11" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="B132" t="inlineStr">
@@ -7733,7 +7007,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N137" s="12" t="n"/>
+      <c r="N137" s="11" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="B138" t="inlineStr">
@@ -8061,7 +7335,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N144" s="12" t="n"/>
+      <c r="N144" s="11" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="B145" t="inlineStr">
@@ -8251,7 +7525,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N148" s="13" t="inlineStr">
+      <c r="N148" s="12" t="inlineStr">
         <is>
           <t>Mağusa Şube</t>
         </is>
@@ -8404,11 +7678,1039 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="N7 N11 N14 N17 N20 N23 N27 N30 N35 N39 N42 N45 N51 N57 N60 N63 N70 N74 N77 N84 N87 N94 N97 N100 N107 N110 N113 N117 N121 N128 N131 N137 N144 N148" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Mağusa Şube,Intech Salamis Kiosk"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>GUA COFFEE COMPANY TRADING LTD – Mağusa Şube</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Tarih</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Fiş No</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Açıklama</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Vade</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Tutar (KDV dahil)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>A00000000263729</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="n">
+        <v>46409</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>8925</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>GUS295</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>GUSTEA DEMLİK SİYAH ÇAY 12 KG</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>8925</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>TOPLAM (net)</t>
+        </is>
+      </c>
+      <c r="E7" s="10">
+        <f>E4</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>GUA COFFEE COMPANY TRADING LTD – Intech Salamis Kiosk</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Tarih</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Fiş No</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Açıklama</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Vade</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Tutar (KDV dahil)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Henüz bu şubeye eşleşen fatura yok.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="90" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Şubesi henüz belirlenmemiş faturalar (teslim fişi / şube bilgisi gerekli)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Tarih</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Fiş No</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Tür</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Tutar</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Ürünler</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Şube (doldur)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>A00000000242321</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>3960</v>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.) x1; BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.) x1</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A00000000242322</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>1980</v>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI FRAMBUAZ 4 KG KL/4AD x1</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>A00000000242346</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>870</v>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>TEAJOY KONT.BAZ PLASTİK POMPASI x5</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>A00000000242518</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>1190.25</v>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>PİPET KAĞIT BYZ BUBBLE 12X24 PK/75AD KL/14PK x10</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>A00000000242620</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>11550</v>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>GUA İKİLİ TAŞIYICI PK/100 ADETLİ x1000</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A00000000243183</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>1291.13</v>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>TEAJOY KONT.BAZ PLASTİK POMPASI x4; PİPET KAĞIT BYZ BUBBLE 12X24 PK/75AD KL/14PK x5</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A00000000244577</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>33852</v>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>GUA RAMAZAN 14 OZ DW KARTON BARDAK KL/500AD x10000</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A00000000246358</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>6153.59</v>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>GUSSE MEY.PÜRE 1,1LT  YABAN MERSİNİ x1; BOBAJOY MEYVE SUYU TOPLARI YEŞİL ELMA 4KG KL/4AD (2.) x1; BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.) x1</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>A00000000246493</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>5509.88</v>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>GUA BASKILI 22X11X28 KRAFT DÜZ SAP KL/300 x250; GUSSE MEY.PÜRE 1,1LT  BÖĞÜRTLEN x1</t>
+        </is>
+      </c>
+      <c r="F12" s="18" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>A00000000246753</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>4158</v>
+      </c>
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>GUSSE MEY.PÜRE 1,1LT  BÖĞÜRTLEN x6</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>I00000000246861</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>IADE FATURANIZ</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>-916.49</v>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>GUSSE MEY.PÜRE 1,1LT  YABAN MERSİNİ x1</t>
+        </is>
+      </c>
+      <c r="F14" s="18" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>A00000000248046</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>8118</v>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>GUSSE MEY.PÜRE 1,1LT  BÖĞÜRTLEN x6; BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.) x1; BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.) x1</t>
+        </is>
+      </c>
+      <c r="F15" s="18" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>A00000000249366</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>7920</v>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>BOBAJOY TOPLARI MANGO 4KG KL/4AD (2.) x1; BOBAJOY MEYVE SUYU TOPLARI YEŞİL ELMA 4KG KL/4AD (2.) x1; BOBAJOY TOPLARI KARAMEL 4 KG KL/4AD (3.) x1; TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD x2</t>
+        </is>
+      </c>
+      <c r="F16" s="18" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>A00000000250156</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>3960</v>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.) x2</t>
+        </is>
+      </c>
+      <c r="F17" s="18" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>A00000000250895</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>5780.25</v>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>GUA BASKILI 22X11X28 KRAFT DÜZ SAP KL/300 x300</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>A00000000251139</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>8910</v>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>BOBAJOY TOPLARI KARAMEL 4 KG KL/4AD (3.) x1; BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.) x1; BOBAJOY TOPLARI MANGO 4KG KL/4AD (2.) x1; TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD x1; BOBAJOY MEYVE SUYU TOPLARI FRAMBUAZ 4 KG KL/4AD x1</t>
+        </is>
+      </c>
+      <c r="F19" s="18" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>A00000000251140</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>1980</v>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>TEAJOY MR.ORGO (MANGO&amp;PRTKL) 2,5 KG KL/4AD x1; TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD x1</t>
+        </is>
+      </c>
+      <c r="F20" s="18" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>A00000000252956</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>1980</v>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.) x1</t>
+        </is>
+      </c>
+      <c r="F21" s="18" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>A00000000253718</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>9900</v>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.) x1; BOBAJOY TOPLARI KARAMEL 4 KG KL/4AD (3.) x1; BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.) x1; BOBAJOY TOPLARI MANGO 4KG KL/4AD (2.) x1; TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD x2</t>
+        </is>
+      </c>
+      <c r="F22" s="18" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>A00000000254148</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>1980</v>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD x2</t>
+        </is>
+      </c>
+      <c r="F23" s="18" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>A00000000254821</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>19469.6</v>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI YEŞİL ELMA 4KG KL/4AD (2.) x1; BOBAJOY TOPLARI MANGO 4KG KL/4AD (2.) x1; BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.) x1; TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD x1; BİO PİPET BEYAZ 7X22  PK/250AD KL/20 PK x40</t>
+        </is>
+      </c>
+      <c r="F24" s="18" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>A00000000254951</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>12992</v>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>BİO PİPET BEYAZ 8X24 SARGILI PK/250AD KL/20 x40</t>
+        </is>
+      </c>
+      <c r="F25" s="18" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>I00000000255472</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>IADE FATURANIZ</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>-12539.6</v>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>BİO PİPET BEYAZ 7X22  PK/250AD KL/20 PK x40</t>
+        </is>
+      </c>
+      <c r="F26" s="18" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="16" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>A00000000255781</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>14250</v>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>GUA BASKILI 22X11X28 KRAFT DÜZ SAP KL/300 x600; BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.) x1; BOBAJOY TOPLARI KARAMEL 4 KG KL/4AD (3.) x1; TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD x3; TEAJOY MR.ORGO (MANGO&amp;PRTKL) 2,5 KG KL/4AD x2</t>
+        </is>
+      </c>
+      <c r="F27" s="18" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>A00000000255791</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>495</v>
+      </c>
+      <c r="E28" s="17" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI Y.MERSİNİ 1KG KL/12AD x1</t>
+        </is>
+      </c>
+      <c r="F28" s="18" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>A00000000256524</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>4640</v>
+      </c>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>PİPET KAĞIT BEYAZ 12X21 SARGILI PK/200AD KL/10PK x10</t>
+        </is>
+      </c>
+      <c r="F29" s="18" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>A00000000257286</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>1848</v>
+      </c>
+      <c r="E30" s="17" t="inlineStr">
+        <is>
+          <t>TEAJOY MR.ORGO (MANGO&amp;PRTKL) 2,5 KG KL/4AD x1; TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD x1</t>
+        </is>
+      </c>
+      <c r="F30" s="18" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>A00000000257723</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>5940</v>
+      </c>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>BOBAJOY TOPLARI KARAMEL 4 KG KL/4AD (3.) x2; BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.) x1</t>
+        </is>
+      </c>
+      <c r="F31" s="18" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>A00000000259067</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>7920</v>
+      </c>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.) x1; BOBAJOY MEYVE SUYU TOPLARI MANGO 4KG KL/4AD x1; BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.) x1; BOBAJOY MEYVE SUYU TOPLARI YEŞİL ELMA 4KG KL/4AD (2.) x1</t>
+        </is>
+      </c>
+      <c r="F32" s="18" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>A00000000259115</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>1848</v>
+      </c>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD x2</t>
+        </is>
+      </c>
+      <c r="F33" s="18" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>A00000000259123</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>20481.41</v>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.) x2; BOBAJOY MEYVE SUYU TOPLARI MANGO 4KG KL/4AD x1; BİO PİPET BEYAZ 8X24 SARGILI PK/250AD KL/20 x40; TEAJOY MR.ORGO (MANGO&amp;PRTKL) 2,5 KG KL/4AD x2</t>
+        </is>
+      </c>
+      <c r="F34" s="18" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>A00000000259190</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>13285</v>
+      </c>
+      <c r="E35" s="17" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.) x1; BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.) x1; BOBAJOY MEYVE SUYU TOPLARI YEŞİL ELMA 4KG KL/4AD (2.) x1; BOBAJOY MEYVE SUYU TOPLARI MANGO 4KG KL/4AD x1; BİO PİPET BEYAZ 6X23 SARGILI PK/200AD KL/25 x25</t>
+        </is>
+      </c>
+      <c r="F35" s="18" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>A00000000263425</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>3555</v>
+      </c>
+      <c r="E36" s="17" t="inlineStr">
+        <is>
+          <t>BOBAJOY TOPLARI KARAMEL 4 KG KL/4AD (3.) x1; 14 OZ BEYAZ DÜZ KAPAK KL/1000 x1000</t>
+        </is>
+      </c>
+      <c r="F36" s="18" t="n"/>
+    </row>
+    <row r="38">
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>TOPLAM (net)</t>
+        </is>
+      </c>
+      <c r="D38" s="1">
+        <f>SUM(D4:D36)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/GUA_Sube_Dokum.xlsx
+++ b/GUA_Sube_Dokum.xlsx
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>8925</v>
+        <v>29406.41</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>0</v>
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>227767.11</v>
+        <v>207285.7</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>13456.09</v>
@@ -6725,7 +6725,11 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N131" s="11" t="inlineStr"/>
+      <c r="N131" s="12" t="inlineStr">
+        <is>
+          <t>Mağusa Şube</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="B132" t="inlineStr">
@@ -7688,7 +7692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7734,11 +7738,11 @@
     </row>
     <row r="4">
       <c r="A4" s="13" t="n">
-        <v>46319</v>
+        <v>46263</v>
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>A00000000263729</t>
+          <t>A00000000259123</t>
         </is>
       </c>
       <c r="C4" s="14" t="inlineStr">
@@ -7747,40 +7751,141 @@
         </is>
       </c>
       <c r="D4" s="13" t="n">
-        <v>46409</v>
+        <v>46353</v>
       </c>
       <c r="E4" s="15" t="n">
-        <v>8925</v>
+        <v>20481.41</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
+          <t>ATM038</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2-AD</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>3960</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ATM040</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI MANGO 4KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PTS038</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BİO PİPET BEYAZ 8X24 SARGILI PK/250AD KL/20</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>40-PK</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>12561.41</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ATM074</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TEAJOY MR.ORGO (MANGO&amp;PRTKL) 2,5 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2-AD</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>A00000000263729</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>46409</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>8925</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
           <t>GUS295</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>GUSTEA DEMLİK SİYAH ÇAY 12 KG</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>1-AD</t>
         </is>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="E10" s="1" t="n">
         <v>8925</v>
       </c>
     </row>
-    <row r="7">
-      <c r="C7" s="9" t="inlineStr">
+    <row r="12">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>TOPLAM (net)</t>
         </is>
       </c>
-      <c r="E7" s="10">
-        <f>E4</f>
+      <c r="E12" s="10">
+        <f>E4+E9</f>
         <v/>
       </c>
     </row>
@@ -7857,7 +7962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8629,11 +8734,11 @@
     </row>
     <row r="34">
       <c r="A34" s="16" t="n">
-        <v>46263</v>
+        <v>46266</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>A00000000259123</t>
+          <t>A00000000259190</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -8642,22 +8747,22 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>20481.41</v>
+        <v>13285</v>
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.) x2; BOBAJOY MEYVE SUYU TOPLARI MANGO 4KG KL/4AD x1; BİO PİPET BEYAZ 8X24 SARGILI PK/250AD KL/20 x40; TEAJOY MR.ORGO (MANGO&amp;PRTKL) 2,5 KG KL/4AD x2</t>
+          <t>BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.) x1; BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.) x1; BOBAJOY MEYVE SUYU TOPLARI YEŞİL ELMA 4KG KL/4AD (2.) x1; BOBAJOY MEYVE SUYU TOPLARI MANGO 4KG KL/4AD x1; BİO PİPET BEYAZ 6X23 SARGILI PK/200AD KL/25 x25</t>
         </is>
       </c>
       <c r="F34" s="18" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="16" t="n">
-        <v>46266</v>
+        <v>46315</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>A00000000259190</t>
+          <t>A00000000263425</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -8666,47 +8771,23 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>13285</v>
+        <v>3555</v>
       </c>
       <c r="E35" s="17" t="inlineStr">
         <is>
-          <t>BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.) x1; BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.) x1; BOBAJOY MEYVE SUYU TOPLARI YEŞİL ELMA 4KG KL/4AD (2.) x1; BOBAJOY MEYVE SUYU TOPLARI MANGO 4KG KL/4AD x1; BİO PİPET BEYAZ 6X23 SARGILI PK/200AD KL/25 x25</t>
+          <t>BOBAJOY TOPLARI KARAMEL 4 KG KL/4AD (3.) x1; 14 OZ BEYAZ DÜZ KAPAK KL/1000 x1000</t>
         </is>
       </c>
       <c r="F35" s="18" t="n"/>
     </row>
-    <row r="36">
-      <c r="A36" s="16" t="n">
-        <v>46315</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>A00000000263425</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>FATURAMIZ</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="n">
-        <v>3555</v>
-      </c>
-      <c r="E36" s="17" t="inlineStr">
-        <is>
-          <t>BOBAJOY TOPLARI KARAMEL 4 KG KL/4AD (3.) x1; 14 OZ BEYAZ DÜZ KAPAK KL/1000 x1000</t>
-        </is>
-      </c>
-      <c r="F36" s="18" t="n"/>
-    </row>
-    <row r="38">
-      <c r="C38" s="9" t="inlineStr">
+    <row r="37">
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>TOPLAM (net)</t>
         </is>
       </c>
-      <c r="D38" s="1">
-        <f>SUM(D4:D36)</f>
+      <c r="D37" s="1">
+        <f>SUM(D4:D35)</f>
         <v/>
       </c>
     </row>

--- a/GUA_Sube_Dokum.xlsx
+++ b/GUA_Sube_Dokum.xlsx
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>29406.41</v>
+        <v>52346.41</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>0</v>
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>0</v>
+        <v>24901</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>0</v>
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>207285.7</v>
+        <v>159444.7</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>13456.09</v>
@@ -712,7 +712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N152"/>
+  <dimension ref="A1:O152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -725,6 +725,7 @@
     <col width="9.6640625" bestFit="1" customWidth="1" min="12" max="12"/>
     <col width="11.6640625" bestFit="1" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,6 +810,11 @@
           <t>Şube</t>
         </is>
       </c>
+      <c r="O5" s="9" t="inlineStr">
+        <is>
+          <t>Not (kaynak)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="C6" t="inlineStr">
@@ -864,6 +870,7 @@
         </is>
       </c>
       <c r="N7" s="11" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -1054,6 +1061,7 @@
         </is>
       </c>
       <c r="N11" s="11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -1198,6 +1206,7 @@
         </is>
       </c>
       <c r="N14" s="11" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
@@ -1342,6 +1351,7 @@
         </is>
       </c>
       <c r="N17" s="11" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
@@ -1486,6 +1496,7 @@
         </is>
       </c>
       <c r="N20" s="11" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
@@ -1630,6 +1641,7 @@
         </is>
       </c>
       <c r="N23" s="11" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
@@ -1820,6 +1832,7 @@
         </is>
       </c>
       <c r="N27" s="11" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
@@ -1964,6 +1977,7 @@
         </is>
       </c>
       <c r="N30" s="11" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
@@ -2200,6 +2214,7 @@
         </is>
       </c>
       <c r="N35" s="11" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="B36" t="inlineStr">
@@ -2390,6 +2405,7 @@
         </is>
       </c>
       <c r="N39" s="11" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="B40" t="inlineStr">
@@ -2534,6 +2550,7 @@
         </is>
       </c>
       <c r="N42" s="11" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="B43" t="inlineStr">
@@ -2678,6 +2695,7 @@
         </is>
       </c>
       <c r="N45" s="11" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="B46" t="inlineStr">
@@ -2949,6 +2967,7 @@
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="B52" t="inlineStr">
@@ -3231,6 +3250,7 @@
         </is>
       </c>
       <c r="N57" s="11" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="B58" t="inlineStr">
@@ -3375,6 +3395,7 @@
         </is>
       </c>
       <c r="N60" s="11" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="B61" t="inlineStr">
@@ -3519,6 +3540,7 @@
         </is>
       </c>
       <c r="N63" s="11" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="B64" t="inlineStr">
@@ -3847,6 +3869,7 @@
         </is>
       </c>
       <c r="N70" s="11" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="B71" t="inlineStr">
@@ -4037,6 +4060,7 @@
         </is>
       </c>
       <c r="N74" s="11" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="B75" t="inlineStr">
@@ -4181,6 +4205,7 @@
         </is>
       </c>
       <c r="N77" s="11" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="B78" t="inlineStr">
@@ -4509,6 +4534,7 @@
         </is>
       </c>
       <c r="N84" s="11" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="B85" t="inlineStr">
@@ -4653,6 +4679,7 @@
         </is>
       </c>
       <c r="N87" s="11" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="B88" t="inlineStr">
@@ -4981,6 +5008,7 @@
         </is>
       </c>
       <c r="N94" s="11" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="B95" t="inlineStr">
@@ -5125,6 +5153,7 @@
         </is>
       </c>
       <c r="N97" s="11" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="B98" t="inlineStr">
@@ -5268,7 +5297,16 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N100" s="11" t="inlineStr"/>
+      <c r="N100" s="12" t="inlineStr">
+        <is>
+          <t>Mağusa Şube</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Teslim fişi: Mağusa Şube (elle yazılı; fişte fatura no boş, kalemler eşleşiyor)</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="B101" t="inlineStr">
@@ -5596,7 +5634,16 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N107" s="11" t="inlineStr"/>
+      <c r="N107" s="12" t="inlineStr">
+        <is>
+          <t>Mağusa Şube</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>255781 ile aynı fişte (ATM057 kalemi) – Mağusa Şube; fişte fatura no yok</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="B108" t="inlineStr">
@@ -5740,7 +5787,16 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N110" s="11" t="inlineStr"/>
+      <c r="N110" s="12" t="inlineStr">
+        <is>
+          <t>Mağusa Şube</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>Teslim fişi: MAĞUSA ŞUBE</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="B111" t="inlineStr">
@@ -5884,7 +5940,16 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N113" s="11" t="inlineStr"/>
+      <c r="N113" s="12" t="inlineStr">
+        <is>
+          <t>Intech Salamis Kiosk</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>Teslim fişi: KİOSK</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="B114" t="inlineStr">
@@ -6075,6 +6140,11 @@
         </is>
       </c>
       <c r="N117" s="11" t="inlineStr"/>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>Fiş var ama 'Teslim Şubesi' boş bırakılmış</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="B118" t="inlineStr">
@@ -6264,7 +6334,16 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N121" s="11" t="inlineStr"/>
+      <c r="N121" s="12" t="inlineStr">
+        <is>
+          <t>Intech Salamis Kiosk</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>Teslim fişi: INTECH SALAMIS KIOSK ŞUBESİ</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="B122" t="inlineStr">
@@ -6581,7 +6660,16 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N128" s="11" t="inlineStr"/>
+      <c r="N128" s="12" t="inlineStr">
+        <is>
+          <t>Intech Salamis Kiosk</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>Teslim fişi: INTECH SALAMIS KIOSK ŞUBESİ</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="B129" t="inlineStr">
@@ -6730,6 +6818,11 @@
           <t>Mağusa Şube</t>
         </is>
       </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>Teslim fişi: MERKEZ MAĞUSA ŞUBESİ</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="B132" t="inlineStr">
@@ -7011,7 +7104,16 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N137" s="11" t="inlineStr"/>
+      <c r="N137" s="12" t="inlineStr">
+        <is>
+          <t>Intech Salamis Kiosk</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>Teslim fişi: INTECH SALAMIS KIOSK ŞUBESİ</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="B138" t="inlineStr">
@@ -7339,7 +7441,16 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N144" s="11" t="inlineStr"/>
+      <c r="N144" s="12" t="inlineStr">
+        <is>
+          <t>Mağusa Şube</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>Teslim fişi: MAĞUSA ŞUBESİ</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="B145" t="inlineStr">
@@ -7532,6 +7643,11 @@
       <c r="N148" s="12" t="inlineStr">
         <is>
           <t>Mağusa Şube</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Teslim fişi: MAĞUSA</t>
         </is>
       </c>
     </row>
@@ -7692,7 +7808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7700,6 +7816,7 @@
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7735,14 +7852,19 @@
           <t>Tutar (KDV dahil)</t>
         </is>
       </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Not (kaynak)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="n">
-        <v>46263</v>
+        <v>46223</v>
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>A00000000259123</t>
+          <t>A00000000255781</t>
         </is>
       </c>
       <c r="C4" s="14" t="inlineStr">
@@ -7751,41 +7873,46 @@
         </is>
       </c>
       <c r="D4" s="13" t="n">
-        <v>46353</v>
+        <v>46313</v>
       </c>
       <c r="E4" s="15" t="n">
-        <v>20481.41</v>
+        <v>14250</v>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>Teslim fişi: Mağusa Şube (elle yazılı; fişte fatura no boş, kalemler eşleşiyor)</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>ATM038</t>
+          <t>MRS0010</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.)</t>
+          <t>GUA BASKILI 22X11X28 KRAFT DÜZ SAP KL/300</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2-AD</t>
+          <t>600-AD</t>
         </is>
       </c>
       <c r="E5" s="1" t="n">
-        <v>3960</v>
+        <v>5670</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>ATM040</t>
+          <t>ATM017</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BOBAJOY MEYVE SUYU TOPLARI MANGO 4KG KL/4AD</t>
+          <t>BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7800,92 +7927,381 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>PTS038</t>
+          <t>ATM033</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BİO PİPET BEYAZ 8X24 SARGILI PK/250AD KL/20</t>
+          <t>BOBAJOY TOPLARI KARAMEL 4 KG KL/4AD (3.)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>40-PK</t>
+          <t>1-AD</t>
         </is>
       </c>
       <c r="E7" s="1" t="n">
-        <v>12561.41</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
+          <t>ATM070</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3-AD</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>2772</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
           <t>ATM074</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>TEAJOY MR.ORGO (MANGO&amp;PRTKL) 2,5 KG KL/4AD</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>2-AD</t>
         </is>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="E9" s="1" t="n">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>A00000000255791</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>46313</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>495</v>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>255781 ile aynı fişte (ATM057 kalemi) – Mağusa Şube; fişte fatura no yok</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ATM057</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI Y.MERSİNİ 1KG KL/12AD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>A00000000256524</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>46320</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>4640</v>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>Teslim fişi: MAĞUSA ŞUBE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CK001</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PİPET KAĞIT BEYAZ 12X21 SARGILI PK/200AD KL/10PK</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>10-PK</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>4640</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>A00000000259123</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>46353</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>20481.41</v>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>Teslim fişi: MERKEZ MAĞUSA ŞUBESİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ATM038</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2-AD</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>3960</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ATM040</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI MANGO 4KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="n">
         <v>1980</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="13" t="n">
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PTS038</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BİO PİPET BEYAZ 8X24 SARGILI PK/250AD KL/20</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>40-PK</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>12561.41</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ATM074</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>TEAJOY MR.ORGO (MANGO&amp;PRTKL) 2,5 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2-AD</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>A00000000263425</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="n">
+        <v>46405</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>3555</v>
+      </c>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>Teslim fişi: MAĞUSA ŞUBESİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ATM033</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BOBAJOY TOPLARI KARAMEL 4 KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BBT028</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>14 OZ BEYAZ DÜZ KAPAK KL/1000</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1000-AD</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="n">
         <v>46319</v>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>A00000000263729</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>FATURAMIZ</t>
         </is>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D22" s="13" t="n">
         <v>46409</v>
       </c>
-      <c r="E9" s="15" t="n">
+      <c r="E22" s="15" t="n">
         <v>8925</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>Teslim fişi: MAĞUSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
         <is>
           <t>GUS295</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>GUSTEA DEMLİK SİYAH ÇAY 12 KG</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>1-AD</t>
         </is>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="E23" s="1" t="n">
         <v>8925</v>
       </c>
     </row>
-    <row r="12">
-      <c r="C12" s="9" t="inlineStr">
+    <row r="25">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>TOPLAM (net)</t>
         </is>
       </c>
-      <c r="E12" s="10">
-        <f>E4+E9</f>
+      <c r="E25" s="10">
+        <f>E4+E10+E12+E14+E19+E22</f>
         <v/>
       </c>
     </row>
@@ -7900,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7908,6 +8324,7 @@
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7943,12 +8360,365 @@
           <t>Tutar (KDV dahil)</t>
         </is>
       </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Not (kaynak)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>A00000000257286</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="n">
+        <v>46330</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>1848</v>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>Teslim fişi: KİOSK</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Henüz bu şubeye eşleşen fatura yok.</t>
-        </is>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ATM074</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TEAJOY MR.ORGO (MANGO&amp;PRTKL) 2,5 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ATM070</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>A00000000259067</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>46352</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>7920</v>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>Teslim fişi: INTECH SALAMIS KIOSK ŞUBESİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ATM017</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ATM040</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI MANGO 4KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ATM038</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ATM030</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI YEŞİL ELMA 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>A00000000259115</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>46353</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>1848</v>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>Teslim fişi: INTECH SALAMIS KIOSK ŞUBESİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ATM070</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2-AD</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>A00000000259190</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>46356</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>13285</v>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>Teslim fişi: INTECH SALAMIS KIOSK ŞUBESİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ATM017</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ATM038</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ATM030</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI YEŞİL ELMA 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ATM040</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI MANGO 4KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PTS032</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BİO PİPET BEYAZ 6X23 SARGILI PK/200AD KL/25</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>25-PK</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>5365</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>TOPLAM (net)</t>
+        </is>
+      </c>
+      <c r="E21" s="10">
+        <f>E4+E7+E12+E14</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -7962,7 +8732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7971,6 +8741,7 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="90" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8011,6 +8782,11 @@
           <t>Şube (doldur)</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Not</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="n">
@@ -8035,6 +8811,7 @@
         </is>
       </c>
       <c r="F4" s="18" t="n"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="16" t="n">
@@ -8059,6 +8836,7 @@
         </is>
       </c>
       <c r="F5" s="18" t="n"/>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="16" t="n">
@@ -8083,6 +8861,7 @@
         </is>
       </c>
       <c r="F6" s="18" t="n"/>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="16" t="n">
@@ -8107,6 +8886,7 @@
         </is>
       </c>
       <c r="F7" s="18" t="n"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="16" t="n">
@@ -8131,6 +8911,7 @@
         </is>
       </c>
       <c r="F8" s="18" t="n"/>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="16" t="n">
@@ -8155,6 +8936,7 @@
         </is>
       </c>
       <c r="F9" s="18" t="n"/>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="16" t="n">
@@ -8179,6 +8961,7 @@
         </is>
       </c>
       <c r="F10" s="18" t="n"/>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="16" t="n">
@@ -8203,6 +8986,7 @@
         </is>
       </c>
       <c r="F11" s="18" t="n"/>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="16" t="n">
@@ -8227,6 +9011,7 @@
         </is>
       </c>
       <c r="F12" s="18" t="n"/>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="16" t="n">
@@ -8251,6 +9036,7 @@
         </is>
       </c>
       <c r="F13" s="18" t="n"/>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="16" t="n">
@@ -8275,6 +9061,7 @@
         </is>
       </c>
       <c r="F14" s="18" t="n"/>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="16" t="n">
@@ -8299,6 +9086,7 @@
         </is>
       </c>
       <c r="F15" s="18" t="n"/>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="16" t="n">
@@ -8323,6 +9111,7 @@
         </is>
       </c>
       <c r="F16" s="18" t="n"/>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="16" t="n">
@@ -8347,6 +9136,7 @@
         </is>
       </c>
       <c r="F17" s="18" t="n"/>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="16" t="n">
@@ -8371,6 +9161,7 @@
         </is>
       </c>
       <c r="F18" s="18" t="n"/>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="16" t="n">
@@ -8395,6 +9186,7 @@
         </is>
       </c>
       <c r="F19" s="18" t="n"/>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="16" t="n">
@@ -8419,6 +9211,7 @@
         </is>
       </c>
       <c r="F20" s="18" t="n"/>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="16" t="n">
@@ -8443,6 +9236,7 @@
         </is>
       </c>
       <c r="F21" s="18" t="n"/>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="16" t="n">
@@ -8467,6 +9261,7 @@
         </is>
       </c>
       <c r="F22" s="18" t="n"/>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="16" t="n">
@@ -8491,6 +9286,7 @@
         </is>
       </c>
       <c r="F23" s="18" t="n"/>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="16" t="n">
@@ -8515,6 +9311,7 @@
         </is>
       </c>
       <c r="F24" s="18" t="n"/>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="16" t="n">
@@ -8539,6 +9336,7 @@
         </is>
       </c>
       <c r="F25" s="18" t="n"/>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="16" t="n">
@@ -8563,14 +9361,15 @@
         </is>
       </c>
       <c r="F26" s="18" t="n"/>
+      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="16" t="n">
-        <v>46223</v>
+        <v>46245</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>A00000000255781</t>
+          <t>A00000000257723</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -8579,215 +9378,28 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>14250</v>
+        <v>5940</v>
       </c>
       <c r="E27" s="17" t="inlineStr">
         <is>
-          <t>GUA BASKILI 22X11X28 KRAFT DÜZ SAP KL/300 x600; BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.) x1; BOBAJOY TOPLARI KARAMEL 4 KG KL/4AD (3.) x1; TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD x3; TEAJOY MR.ORGO (MANGO&amp;PRTKL) 2,5 KG KL/4AD x2</t>
+          <t>BOBAJOY TOPLARI KARAMEL 4 KG KL/4AD (3.) x2; BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.) x1</t>
         </is>
       </c>
       <c r="F27" s="18" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="16" t="n">
-        <v>46223</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>A00000000255791</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>FATURAMIZ</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>495</v>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>BOBAJOY MEYVE SUYU TOPLARI Y.MERSİNİ 1KG KL/12AD x1</t>
-        </is>
-      </c>
-      <c r="F28" s="18" t="n"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Fiş var ama 'Teslim Şubesi' boş bırakılmış</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="n">
-        <v>46230</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>A00000000256524</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>FATURAMIZ</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>4640</v>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>PİPET KAĞIT BEYAZ 12X21 SARGILI PK/200AD KL/10PK x10</t>
-        </is>
-      </c>
-      <c r="F29" s="18" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="16" t="n">
-        <v>46240</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>A00000000257286</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>FATURAMIZ</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>1848</v>
-      </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>TEAJOY MR.ORGO (MANGO&amp;PRTKL) 2,5 KG KL/4AD x1; TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD x1</t>
-        </is>
-      </c>
-      <c r="F30" s="18" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="16" t="n">
-        <v>46245</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>A00000000257723</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>FATURAMIZ</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>5940</v>
-      </c>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>BOBAJOY TOPLARI KARAMEL 4 KG KL/4AD (3.) x2; BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.) x1</t>
-        </is>
-      </c>
-      <c r="F31" s="18" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="16" t="n">
-        <v>46262</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>A00000000259067</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>FATURAMIZ</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>7920</v>
-      </c>
-      <c r="E32" s="17" t="inlineStr">
-        <is>
-          <t>BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.) x1; BOBAJOY MEYVE SUYU TOPLARI MANGO 4KG KL/4AD x1; BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.) x1; BOBAJOY MEYVE SUYU TOPLARI YEŞİL ELMA 4KG KL/4AD (2.) x1</t>
-        </is>
-      </c>
-      <c r="F32" s="18" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="16" t="n">
-        <v>46263</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>A00000000259115</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>FATURAMIZ</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>1848</v>
-      </c>
-      <c r="E33" s="17" t="inlineStr">
-        <is>
-          <t>TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD x2</t>
-        </is>
-      </c>
-      <c r="F33" s="18" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="16" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>A00000000259190</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>FATURAMIZ</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>13285</v>
-      </c>
-      <c r="E34" s="17" t="inlineStr">
-        <is>
-          <t>BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.) x1; BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.) x1; BOBAJOY MEYVE SUYU TOPLARI YEŞİL ELMA 4KG KL/4AD (2.) x1; BOBAJOY MEYVE SUYU TOPLARI MANGO 4KG KL/4AD x1; BİO PİPET BEYAZ 6X23 SARGILI PK/200AD KL/25 x25</t>
-        </is>
-      </c>
-      <c r="F34" s="18" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="16" t="n">
-        <v>46315</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>A00000000263425</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>FATURAMIZ</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>3555</v>
-      </c>
-      <c r="E35" s="17" t="inlineStr">
-        <is>
-          <t>BOBAJOY TOPLARI KARAMEL 4 KG KL/4AD (3.) x1; 14 OZ BEYAZ DÜZ KAPAK KL/1000 x1000</t>
-        </is>
-      </c>
-      <c r="F35" s="18" t="n"/>
-    </row>
-    <row r="37">
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>TOPLAM (net)</t>
         </is>
       </c>
-      <c r="D37" s="1">
-        <f>SUM(D4:D35)</f>
+      <c r="D29" s="1">
+        <f>SUM(D4:D27)</f>
         <v/>
       </c>
     </row>

--- a/GUA_Sube_Dokum.xlsx
+++ b/GUA_Sube_Dokum.xlsx
@@ -7,10 +7,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Özet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detaylı Döküm" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mağusa Şube" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intech Salamis Kiosk" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Şubesiz (Bekleyen)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ürün Özeti" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detaylı Döküm" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mağusa Şube" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intech Salamis Kiosk" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Şubesiz (Bekleyen)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ürün Dökümü" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -19,10 +21,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="dd.mm.yyyy"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="#,##0.##"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -54,12 +57,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00C6E0B4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6E0B4"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -88,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -100,6 +103,8 @@
     <xf numFmtId="166" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -109,7 +114,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -564,10 +569,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>52346.41</v>
+        <v>207831.11</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>0</v>
@@ -588,10 +593,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>24901</v>
+        <v>28861</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>0</v>
@@ -612,10 +617,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>159444.7</v>
+        <v>0</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>13456.09</v>
@@ -707,6 +712,677 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Şube bazında toplam ürün adetleri</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>MAĞUSA ŞUBE</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="n"/>
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Ürün Kodu</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Birim</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Toplam Adet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ATM017</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ATM027</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BOBAJOY TOPLARI MANGO 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ATM030</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI YEŞİL ELMA 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ATM033</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BOBAJOY TOPLARI KARAMEL 4 KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ATM038</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ATM040</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI MANGO 4KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ATM041</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI FRAMBUAZ 4 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ATM057</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI Y.MERSİNİ 1KG KL/12AD</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ATM070</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ATM074</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TEAJOY MR.ORGO (MANGO&amp;PRTKL) 2,5 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ATM076</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TEAJOY KONT.BAZ PLASTİK POMPASI</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BBT028</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>14 OZ BEYAZ DÜZ KAPAK KL/1000</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BBT0302</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>GUA RAMAZAN 14 OZ DW KARTON BARDAK KL/500AD</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CK001</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PİPET KAĞIT BEYAZ 12X21 SARGILI PK/200AD KL/10PK</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FG004</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PİPET KAĞIT BYZ BUBBLE 12X24 PK/75AD KL/14PK</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>GUS123</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>GUSSE MEY.PÜRE 1,1LT  BÖĞÜRTLEN</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>GUS124</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>GUSSE MEY.PÜRE 1,1LT  YABAN MERSİNİ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>GUS295</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>GUSTEA DEMLİK SİYAH ÇAY 12 KG</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MRS0010</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>GUA BASKILI 22X11X28 KRAFT DÜZ SAP KL/300</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="n">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MRS0011</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>GUA İKİLİ TAŞIYICI PK/100 ADETLİ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PTS030</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BİO PİPET BEYAZ 7X22  PK/250AD KL/20 PK</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PTS038</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BİO PİPET BEYAZ 8X24 SARGILI PK/250AD KL/20</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>INTECH SALAMIS KIOSK</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n"/>
+      <c r="C29" s="11" t="n"/>
+      <c r="D29" s="11" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>Ürün Kodu</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Birim</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>Toplam Adet</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ATM017</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ATM030</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI YEŞİL ELMA 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ATM038</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ATM040</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI MANGO 4KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ATM070</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ATM074</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>TEAJOY MR.ORGO (MANGO&amp;PRTKL) 2,5 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PTS032</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BİO PİPET BEYAZ 6X23 SARGILI PK/200AD KL/25</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="n">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -869,8 +1545,16 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N7" s="11" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+      <c r="N7" s="13" t="inlineStr">
+        <is>
+          <t>Mağusa Şube</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -1060,8 +1744,16 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N11" s="11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+      <c r="N11" s="13" t="inlineStr">
+        <is>
+          <t>Mağusa Şube</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -1205,8 +1897,16 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N14" s="11" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="N14" s="13" t="inlineStr">
+        <is>
+          <t>Mağusa Şube</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
@@ -1350,8 +2050,16 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N17" s="11" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+      <c r="N17" s="13" t="inlineStr">
+        <is>
+          <t>Mağusa Şube</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
@@ -1495,8 +2203,16 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N20" s="11" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+      <c r="N20" s="13" t="inlineStr">
+        <is>
+          <t>Mağusa Şube</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
@@ -1640,8 +2356,16 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N23" s="11" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+      <c r="N23" s="13" t="inlineStr">
+        <is>
+          <t>Mağusa Şube</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
@@ -1831,8 +2555,16 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N27" s="11" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
+      <c r="N27" s="13" t="inlineStr">
+        <is>
+          <t>Mağusa Şube</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
@@ -1976,8 +2708,16 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N30" s="11" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
+      <c r="N30" s="13" t="inlineStr">
+        <is>
+          <t>Mağusa Şube</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
@@ -2213,8 +2953,16 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N35" s="11" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+      <c r="N35" s="13" t="inlineStr">
+        <is>
+          <t>Mağusa Şube</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="B36" t="inlineStr">
@@ -2404,8 +3152,16 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N39" s="11" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
+      <c r="N39" s="13" t="inlineStr">
+        <is>
+          <t>Mağusa Şube</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="B40" t="inlineStr">
@@ -2549,7 +3305,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N42" s="11" t="inlineStr"/>
+      <c r="N42" s="14" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
@@ -2694,8 +3450,16 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N45" s="11" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
+      <c r="N45" s="13" t="inlineStr">
+        <is>
+          <t>Mağusa Şube</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="B46" t="inlineStr">
@@ -2966,8 +3730,16 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N51" s="11" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
+      <c r="N51" s="13" t="inlineStr">
+        <is>
+          <t>Mağusa Şube</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="B52" t="inlineStr">
@@ -3249,8 +4021,16 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N57" s="11" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
+      <c r="N57" s="13" t="inlineStr">
+        <is>
+          <t>Mağusa Şube</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="B58" t="inlineStr">
@@ -3394,8 +4174,16 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N60" s="11" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
+      <c r="N60" s="13" t="inlineStr">
+        <is>
+          <t>Mağusa Şube</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="B61" t="inlineStr">
@@ -3539,8 +4327,16 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N63" s="11" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
+      <c r="N63" s="13" t="inlineStr">
+        <is>
+          <t>Mağusa Şube</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="B64" t="inlineStr">
@@ -3868,8 +4664,16 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N70" s="11" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
+      <c r="N70" s="13" t="inlineStr">
+        <is>
+          <t>Intech Salamis Kiosk</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Kiosk)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="B71" t="inlineStr">
@@ -4059,8 +4863,16 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N74" s="11" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
+      <c r="N74" s="13" t="inlineStr">
+        <is>
+          <t>Mağusa Şube</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="B75" t="inlineStr">
@@ -4204,8 +5016,16 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N77" s="11" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
+      <c r="N77" s="13" t="inlineStr">
+        <is>
+          <t>Mağusa Şube</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="B78" t="inlineStr">
@@ -4533,8 +5353,16 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N84" s="11" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
+      <c r="N84" s="13" t="inlineStr">
+        <is>
+          <t>Intech Salamis Kiosk</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Kiosk)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="B85" t="inlineStr">
@@ -4678,8 +5506,16 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N87" s="11" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
+      <c r="N87" s="13" t="inlineStr">
+        <is>
+          <t>Mağusa Şube</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="B88" t="inlineStr">
@@ -5007,8 +5843,16 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N94" s="11" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
+      <c r="N94" s="13" t="inlineStr">
+        <is>
+          <t>Mağusa Şube</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="B95" t="inlineStr">
@@ -5152,7 +5996,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N97" s="11" t="inlineStr"/>
+      <c r="N97" s="14" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
     </row>
     <row r="98">
@@ -5297,7 +6141,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N100" s="12" t="inlineStr">
+      <c r="N100" s="13" t="inlineStr">
         <is>
           <t>Mağusa Şube</t>
         </is>
@@ -5634,7 +6478,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N107" s="12" t="inlineStr">
+      <c r="N107" s="13" t="inlineStr">
         <is>
           <t>Mağusa Şube</t>
         </is>
@@ -5787,7 +6631,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N110" s="12" t="inlineStr">
+      <c r="N110" s="13" t="inlineStr">
         <is>
           <t>Mağusa Şube</t>
         </is>
@@ -5940,7 +6784,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N113" s="12" t="inlineStr">
+      <c r="N113" s="13" t="inlineStr">
         <is>
           <t>Intech Salamis Kiosk</t>
         </is>
@@ -6139,10 +6983,14 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N117" s="11" t="inlineStr"/>
+      <c r="N117" s="13" t="inlineStr">
+        <is>
+          <t>Mağusa Şube</t>
+        </is>
+      </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Fiş var ama 'Teslim Şubesi' boş bırakılmış</t>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa); fişte şube boş</t>
         </is>
       </c>
     </row>
@@ -6334,7 +7182,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N121" s="12" t="inlineStr">
+      <c r="N121" s="13" t="inlineStr">
         <is>
           <t>Intech Salamis Kiosk</t>
         </is>
@@ -6660,7 +7508,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N128" s="12" t="inlineStr">
+      <c r="N128" s="13" t="inlineStr">
         <is>
           <t>Intech Salamis Kiosk</t>
         </is>
@@ -6813,7 +7661,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N131" s="12" t="inlineStr">
+      <c r="N131" s="13" t="inlineStr">
         <is>
           <t>Mağusa Şube</t>
         </is>
@@ -7104,7 +7952,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N137" s="12" t="inlineStr">
+      <c r="N137" s="13" t="inlineStr">
         <is>
           <t>Intech Salamis Kiosk</t>
         </is>
@@ -7441,7 +8289,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N144" s="12" t="inlineStr">
+      <c r="N144" s="13" t="inlineStr">
         <is>
           <t>Mağusa Şube</t>
         </is>
@@ -7640,7 +8488,7 @@
           <t>MRK</t>
         </is>
       </c>
-      <c r="N148" s="12" t="inlineStr">
+      <c r="N148" s="13" t="inlineStr">
         <is>
           <t>Mağusa Şube</t>
         </is>
@@ -7802,13 +8650,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7859,49 +8707,49 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="n">
-        <v>46223</v>
-      </c>
-      <c r="B4" s="14" t="inlineStr">
-        <is>
-          <t>A00000000255781</t>
-        </is>
-      </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="A4" s="15" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>A00000000242321</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>FATURAMIZ</t>
         </is>
       </c>
-      <c r="D4" s="13" t="n">
-        <v>46313</v>
-      </c>
-      <c r="E4" s="15" t="n">
-        <v>14250</v>
-      </c>
-      <c r="F4" s="14" t="inlineStr">
-        <is>
-          <t>Teslim fişi: Mağusa Şube (elle yazılı; fişte fatura no boş, kalemler eşleşiyor)</t>
+      <c r="D4" s="15" t="n">
+        <v>46080</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>3960</v>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>MRS0010</t>
+          <t>ATM038</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GUA BASKILI 22X11X28 KRAFT DÜZ SAP KL/300</t>
+          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>600-AD</t>
+          <t>1-AD</t>
         </is>
       </c>
       <c r="E5" s="1" t="n">
-        <v>5670</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="6">
@@ -7925,383 +8773,1763 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ATM033</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>BOBAJOY TOPLARI KARAMEL 4 KG KL/4AD (3.)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1-AD</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="n">
+      <c r="A7" s="15" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>A00000000242322</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>46080</v>
+      </c>
+      <c r="E7" s="17" t="n">
         <v>1980</v>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>ATM070</t>
+          <t>ATM041</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD</t>
+          <t>BOBAJOY MEYVE SUYU TOPLARI FRAMBUAZ 4 KG KL/4AD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3-AD</t>
+          <t>1-AD</t>
         </is>
       </c>
       <c r="E8" s="1" t="n">
-        <v>2772</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ATM074</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>TEAJOY MR.ORGO (MANGO&amp;PRTKL) 2,5 KG KL/4AD</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2-AD</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>1848</v>
+      <c r="A9" s="15" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>A00000000242346</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>46081</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>870</v>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="n">
-        <v>46223</v>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>A00000000255791</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ATM076</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TEAJOY KONT.BAZ PLASTİK POMPASI</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>5-AD</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>A00000000242518</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>FATURAMIZ</t>
         </is>
       </c>
-      <c r="D10" s="13" t="n">
-        <v>46313</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>495</v>
-      </c>
-      <c r="F10" s="14" t="inlineStr">
-        <is>
-          <t>255781 ile aynı fişte (ATM057 kalemi) – Mağusa Şube; fişte fatura no yok</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ATM057</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>BOBAJOY MEYVE SUYU TOPLARI Y.MERSİNİ 1KG KL/12AD</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1-AD</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>495</v>
+      <c r="D11" s="15" t="n">
+        <v>46085</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>1190.25</v>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="n">
-        <v>46230</v>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>A00000000256524</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>FG004</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PİPET KAĞIT BYZ BUBBLE 12X24 PK/75AD KL/14PK</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>10-PK</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>1190.25</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>A00000000242620</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>FATURAMIZ</t>
         </is>
       </c>
-      <c r="D12" s="13" t="n">
-        <v>46320</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>4640</v>
-      </c>
-      <c r="F12" s="14" t="inlineStr">
-        <is>
-          <t>Teslim fişi: MAĞUSA ŞUBE</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>CK001</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>PİPET KAĞIT BEYAZ 12X21 SARGILI PK/200AD KL/10PK</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>10-PK</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>4640</v>
+      <c r="D13" s="15" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>11550</v>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="n">
-        <v>46263</v>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>A00000000259123</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MRS0011</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>GUA İKİLİ TAŞIYICI PK/100 ADETLİ</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1000-AD</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>11550</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>A00000000243183</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>FATURAMIZ</t>
         </is>
       </c>
-      <c r="D14" s="13" t="n">
-        <v>46353</v>
-      </c>
-      <c r="E14" s="15" t="n">
-        <v>20481.41</v>
-      </c>
-      <c r="F14" s="14" t="inlineStr">
-        <is>
-          <t>Teslim fişi: MERKEZ MAĞUSA ŞUBESİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>ATM038</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.)</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2-AD</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>3960</v>
+      <c r="D15" s="15" t="n">
+        <v>46093</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>1291.13</v>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>ATM040</t>
+          <t>ATM076</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BOBAJOY MEYVE SUYU TOPLARI MANGO 4KG KL/4AD</t>
+          <t>TEAJOY KONT.BAZ PLASTİK POMPASI</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1-AD</t>
+          <t>4-AD</t>
         </is>
       </c>
       <c r="E16" s="1" t="n">
-        <v>1980</v>
+        <v>696</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>PTS038</t>
+          <t>FG004</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BİO PİPET BEYAZ 8X24 SARGILI PK/250AD KL/20</t>
+          <t>PİPET KAĞIT BYZ BUBBLE 12X24 PK/75AD KL/14PK</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>40-PK</t>
+          <t>5-PK</t>
         </is>
       </c>
       <c r="E17" s="1" t="n">
-        <v>12561.41</v>
+        <v>595.13</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ATM074</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>TEAJOY MR.ORGO (MANGO&amp;PRTKL) 2,5 KG KL/4AD</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2-AD</t>
-        </is>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>1980</v>
+      <c r="A18" s="15" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>A00000000244577</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="n">
+        <v>46168</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>33852</v>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="n">
-        <v>46315</v>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
-        <is>
-          <t>A00000000263425</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BBT0302</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>GUA RAMAZAN 14 OZ DW KARTON BARDAK KL/500AD</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>10000-AD</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>33852</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>A00000000246358</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>FATURAMIZ</t>
         </is>
       </c>
-      <c r="D19" s="13" t="n">
-        <v>46405</v>
-      </c>
-      <c r="E19" s="15" t="n">
-        <v>3555</v>
-      </c>
-      <c r="F19" s="14" t="inlineStr">
-        <is>
-          <t>Teslim fişi: MAĞUSA ŞUBESİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ATM033</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>BOBAJOY TOPLARI KARAMEL 4 KG KL/4AD (3.)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>1-AD</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>1980</v>
+      <c r="D20" s="15" t="n">
+        <v>46196</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>6153.59</v>
+      </c>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>BBT028</t>
+          <t>GUS124</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>14 OZ BEYAZ DÜZ KAPAK KL/1000</t>
+          <t>GUSSE MEY.PÜRE 1,1LT  YABAN MERSİNİ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1000-AD</t>
+          <t>1-AD</t>
         </is>
       </c>
       <c r="E21" s="1" t="n">
-        <v>1575</v>
+        <v>916.49</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t>A00000000263729</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="inlineStr">
-        <is>
-          <t>FATURAMIZ</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="n">
-        <v>46409</v>
-      </c>
-      <c r="E22" s="15" t="n">
-        <v>8925</v>
-      </c>
-      <c r="F22" s="14" t="inlineStr">
-        <is>
-          <t>Teslim fişi: MAĞUSA</t>
-        </is>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ATM030</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI YEŞİL ELMA 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>2618.55</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
+          <t>ATM038</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>2618.55</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>A00000000246493</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="n">
+        <v>46198</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>5509.88</v>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MRS0010</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>GUA BASKILI 22X11X28 KRAFT DÜZ SAP KL/300</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>250-AD</t>
+        </is>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>4816.88</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>GUS123</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>GUSSE MEY.PÜRE 1,1LT  BÖĞÜRTLEN</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>A00000000246753</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="n">
+        <v>46198</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>4158</v>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>GUS123</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>GUSSE MEY.PÜRE 1,1LT  BÖĞÜRTLEN</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>6-AD</t>
+        </is>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>4158</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>A00000000248046</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="n">
+        <v>46215</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>8118</v>
+      </c>
+      <c r="F29" s="16" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>GUS123</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>GUSSE MEY.PÜRE 1,1LT  BÖĞÜRTLEN</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>6-AD</t>
+        </is>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>4158</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ATM017</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ATM038</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>A00000000249366</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>7920</v>
+      </c>
+      <c r="F33" s="16" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ATM027</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BOBAJOY TOPLARI MANGO 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ATM030</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI YEŞİL ELMA 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ATM033</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>BOBAJOY TOPLARI KARAMEL 4 KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ATM070</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2-AD</t>
+        </is>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>A00000000250156</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>3960</v>
+      </c>
+      <c r="F38" s="16" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ATM038</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2-AD</t>
+        </is>
+      </c>
+      <c r="E39" s="1" t="n">
+        <v>3960</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>A00000000250895</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D40" s="15" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>5780.25</v>
+      </c>
+      <c r="F40" s="16" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>MRS0010</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>GUA BASKILI 22X11X28 KRAFT DÜZ SAP KL/300</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>300-AD</t>
+        </is>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>5780.25</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>A00000000251139</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>8910</v>
+      </c>
+      <c r="F42" s="16" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ATM033</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>BOBAJOY TOPLARI KARAMEL 4 KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ATM017</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E44" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ATM027</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>BOBAJOY TOPLARI MANGO 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ATM070</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ATM041</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI FRAMBUAZ 4 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B48" s="16" t="inlineStr">
+        <is>
+          <t>A00000000252956</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="n">
+        <v>46275</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>1980</v>
+      </c>
+      <c r="F48" s="16" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ATM038</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E49" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="15" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B50" s="16" t="inlineStr">
+        <is>
+          <t>A00000000253718</t>
+        </is>
+      </c>
+      <c r="C50" s="16" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D50" s="15" t="n">
+        <v>46286</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>9900</v>
+      </c>
+      <c r="F50" s="16" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ATM017</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E51" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ATM033</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>BOBAJOY TOPLARI KARAMEL 4 KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E52" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ATM038</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E53" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ATM027</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>BOBAJOY TOPLARI MANGO 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E54" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ATM070</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2-AD</t>
+        </is>
+      </c>
+      <c r="E55" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="15" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B56" s="16" t="inlineStr">
+        <is>
+          <t>A00000000254821</t>
+        </is>
+      </c>
+      <c r="C56" s="16" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D56" s="15" t="n">
+        <v>46297</v>
+      </c>
+      <c r="E56" s="17" t="n">
+        <v>19469.6</v>
+      </c>
+      <c r="F56" s="16" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ATM030</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI YEŞİL ELMA 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E57" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ATM027</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>BOBAJOY TOPLARI MANGO 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E58" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ATM038</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E59" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>ATM070</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E60" s="1" t="n">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>PTS030</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>BİO PİPET BEYAZ 7X22  PK/250AD KL/20 PK</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>40-PK</t>
+        </is>
+      </c>
+      <c r="E61" s="1" t="n">
+        <v>12539.6</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="15" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B62" s="16" t="inlineStr">
+        <is>
+          <t>A00000000254951</t>
+        </is>
+      </c>
+      <c r="C62" s="16" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D62" s="15" t="n">
+        <v>46300</v>
+      </c>
+      <c r="E62" s="17" t="n">
+        <v>12992</v>
+      </c>
+      <c r="F62" s="16" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>PTS038</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>BİO PİPET BEYAZ 8X24 SARGILI PK/250AD KL/20</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>40-PK</t>
+        </is>
+      </c>
+      <c r="E63" s="1" t="n">
+        <v>12992</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="15" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B64" s="16" t="inlineStr">
+        <is>
+          <t>A00000000255781</t>
+        </is>
+      </c>
+      <c r="C64" s="16" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D64" s="15" t="n">
+        <v>46313</v>
+      </c>
+      <c r="E64" s="17" t="n">
+        <v>14250</v>
+      </c>
+      <c r="F64" s="16" t="inlineStr">
+        <is>
+          <t>Teslim fişi: Mağusa Şube (elle yazılı; fişte fatura no boş, kalemler eşleşiyor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>MRS0010</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>GUA BASKILI 22X11X28 KRAFT DÜZ SAP KL/300</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>600-AD</t>
+        </is>
+      </c>
+      <c r="E65" s="1" t="n">
+        <v>5670</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>ATM017</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E66" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ATM033</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>BOBAJOY TOPLARI KARAMEL 4 KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E67" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ATM070</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>3-AD</t>
+        </is>
+      </c>
+      <c r="E68" s="1" t="n">
+        <v>2772</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ATM074</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>TEAJOY MR.ORGO (MANGO&amp;PRTKL) 2,5 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2-AD</t>
+        </is>
+      </c>
+      <c r="E69" s="1" t="n">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="15" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B70" s="16" t="inlineStr">
+        <is>
+          <t>A00000000255791</t>
+        </is>
+      </c>
+      <c r="C70" s="16" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D70" s="15" t="n">
+        <v>46313</v>
+      </c>
+      <c r="E70" s="17" t="n">
+        <v>495</v>
+      </c>
+      <c r="F70" s="16" t="inlineStr">
+        <is>
+          <t>255781 ile aynı fişte (ATM057 kalemi) – Mağusa Şube; fişte fatura no yok</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ATM057</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI Y.MERSİNİ 1KG KL/12AD</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E71" s="1" t="n">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="15" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B72" s="16" t="inlineStr">
+        <is>
+          <t>A00000000256524</t>
+        </is>
+      </c>
+      <c r="C72" s="16" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D72" s="15" t="n">
+        <v>46320</v>
+      </c>
+      <c r="E72" s="17" t="n">
+        <v>4640</v>
+      </c>
+      <c r="F72" s="16" t="inlineStr">
+        <is>
+          <t>Teslim fişi: MAĞUSA ŞUBE</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CK001</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>PİPET KAĞIT BEYAZ 12X21 SARGILI PK/200AD KL/10PK</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>10-PK</t>
+        </is>
+      </c>
+      <c r="E73" s="1" t="n">
+        <v>4640</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="15" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B74" s="16" t="inlineStr">
+        <is>
+          <t>A00000000257723</t>
+        </is>
+      </c>
+      <c r="C74" s="16" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D74" s="15" t="n">
+        <v>46335</v>
+      </c>
+      <c r="E74" s="17" t="n">
+        <v>5940</v>
+      </c>
+      <c r="F74" s="16" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Merkez/Mağusa); fişte şube boş</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>ATM033</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>BOBAJOY TOPLARI KARAMEL 4 KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2-AD</t>
+        </is>
+      </c>
+      <c r="E75" s="1" t="n">
+        <v>3960</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ATM017</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E76" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="15" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B77" s="16" t="inlineStr">
+        <is>
+          <t>A00000000259123</t>
+        </is>
+      </c>
+      <c r="C77" s="16" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D77" s="15" t="n">
+        <v>46353</v>
+      </c>
+      <c r="E77" s="17" t="n">
+        <v>20481.41</v>
+      </c>
+      <c r="F77" s="16" t="inlineStr">
+        <is>
+          <t>Teslim fişi: MERKEZ MAĞUSA ŞUBESİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ATM038</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2-AD</t>
+        </is>
+      </c>
+      <c r="E78" s="1" t="n">
+        <v>3960</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ATM040</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI MANGO 4KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E79" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PTS038</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>BİO PİPET BEYAZ 8X24 SARGILI PK/250AD KL/20</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>40-PK</t>
+        </is>
+      </c>
+      <c r="E80" s="1" t="n">
+        <v>12561.41</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ATM074</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>TEAJOY MR.ORGO (MANGO&amp;PRTKL) 2,5 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2-AD</t>
+        </is>
+      </c>
+      <c r="E81" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="15" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B82" s="16" t="inlineStr">
+        <is>
+          <t>A00000000263425</t>
+        </is>
+      </c>
+      <c r="C82" s="16" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D82" s="15" t="n">
+        <v>46405</v>
+      </c>
+      <c r="E82" s="17" t="n">
+        <v>3555</v>
+      </c>
+      <c r="F82" s="16" t="inlineStr">
+        <is>
+          <t>Teslim fişi: MAĞUSA ŞUBESİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ATM033</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>BOBAJOY TOPLARI KARAMEL 4 KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E83" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>BBT028</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>14 OZ BEYAZ DÜZ KAPAK KL/1000</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>1000-AD</t>
+        </is>
+      </c>
+      <c r="E84" s="1" t="n">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="15" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B85" s="16" t="inlineStr">
+        <is>
+          <t>A00000000263729</t>
+        </is>
+      </c>
+      <c r="C85" s="16" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D85" s="15" t="n">
+        <v>46409</v>
+      </c>
+      <c r="E85" s="17" t="n">
+        <v>8925</v>
+      </c>
+      <c r="F85" s="16" t="inlineStr">
+        <is>
+          <t>Teslim fişi: MAĞUSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="inlineStr">
+        <is>
           <t>GUS295</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>GUSTEA DEMLİK SİYAH ÇAY 12 KG</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>1-AD</t>
         </is>
       </c>
-      <c r="E23" s="1" t="n">
+      <c r="E86" s="1" t="n">
         <v>8925</v>
       </c>
     </row>
-    <row r="25">
-      <c r="C25" s="9" t="inlineStr">
+    <row r="88">
+      <c r="C88" s="9" t="inlineStr">
         <is>
           <t>TOPLAM (net)</t>
         </is>
       </c>
-      <c r="E25" s="10">
-        <f>E4+E10+E12+E14+E19+E22</f>
+      <c r="E88" s="10">
+        <f>E4+E7+E9+E11+E13+E15+E18+E20+E24+E27+E29+E33+E38+E40+E42+E48+E50+E56+E62+E64+E70+E72+E74+E77+E82+E85</f>
         <v/>
       </c>
     </row>
@@ -8310,13 +10538,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8367,28 +10595,28 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="n">
-        <v>46240</v>
-      </c>
-      <c r="B4" s="14" t="inlineStr">
-        <is>
-          <t>A00000000257286</t>
-        </is>
-      </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="A4" s="15" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>A00000000251140</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>FATURAMIZ</t>
         </is>
       </c>
-      <c r="D4" s="13" t="n">
-        <v>46330</v>
-      </c>
-      <c r="E4" s="15" t="n">
-        <v>1848</v>
-      </c>
-      <c r="F4" s="14" t="inlineStr">
-        <is>
-          <t>Teslim fişi: KİOSK</t>
+      <c r="D4" s="15" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>1980</v>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Kiosk)</t>
         </is>
       </c>
     </row>
@@ -8409,7 +10637,7 @@
         </is>
       </c>
       <c r="E5" s="1" t="n">
-        <v>924</v>
+        <v>990</v>
       </c>
     </row>
     <row r="6">
@@ -8429,49 +10657,49 @@
         </is>
       </c>
       <c r="E6" s="1" t="n">
-        <v>924</v>
+        <v>990</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="n">
-        <v>46262</v>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>A00000000259067</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>A00000000254148</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>FATURAMIZ</t>
         </is>
       </c>
-      <c r="D7" s="13" t="n">
-        <v>46352</v>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>7920</v>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>Teslim fişi: INTECH SALAMIS KIOSK ŞUBESİ</t>
+      <c r="D7" s="15" t="n">
+        <v>46289</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>1980</v>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>Şube bilgisi kullanıcıdan (Kiosk)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>ATM017</t>
+          <t>ATM070</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.)</t>
+          <t>TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1-AD</t>
+          <t>2-AD</t>
         </is>
       </c>
       <c r="E8" s="1" t="n">
@@ -8479,34 +10707,40 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ATM040</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>BOBAJOY MEYVE SUYU TOPLARI MANGO 4KG KL/4AD</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>1-AD</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>1980</v>
+      <c r="A9" s="15" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>A00000000257286</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>46330</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>1848</v>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>Teslim fişi: KİOSK</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>ATM038</t>
+          <t>ATM074</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.)</t>
+          <t>TEAJOY MR.ORGO (MANGO&amp;PRTKL) 2,5 KG KL/4AD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -8515,18 +10749,18 @@
         </is>
       </c>
       <c r="E10" s="1" t="n">
-        <v>1980</v>
+        <v>924</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>ATM030</t>
+          <t>ATM070</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BOBAJOY MEYVE SUYU TOPLARI YEŞİL ELMA 4KG KL/4AD (2.)</t>
+          <t>TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -8535,30 +10769,30 @@
         </is>
       </c>
       <c r="E11" s="1" t="n">
-        <v>1980</v>
+        <v>924</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="n">
-        <v>46263</v>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>A00000000259115</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="A12" s="15" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>A00000000259067</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>FATURAMIZ</t>
         </is>
       </c>
-      <c r="D12" s="13" t="n">
-        <v>46353</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>1848</v>
-      </c>
-      <c r="F12" s="14" t="inlineStr">
+      <c r="D12" s="15" t="n">
+        <v>46352</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>7920</v>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>Teslim fişi: INTECH SALAMIS KIOSK ŞUBESİ</t>
         </is>
@@ -8567,58 +10801,52 @@
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>ATM070</t>
+          <t>ATM017</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD</t>
+          <t>BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2-AD</t>
+          <t>1-AD</t>
         </is>
       </c>
       <c r="E13" s="1" t="n">
-        <v>1848</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>A00000000259190</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>FATURAMIZ</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="n">
-        <v>46356</v>
-      </c>
-      <c r="E14" s="15" t="n">
-        <v>13285</v>
-      </c>
-      <c r="F14" s="14" t="inlineStr">
-        <is>
-          <t>Teslim fişi: INTECH SALAMIS KIOSK ŞUBESİ</t>
-        </is>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ATM040</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI MANGO 4KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>1980</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>ATM017</t>
+          <t>ATM038</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.)</t>
+          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -8633,12 +10861,12 @@
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>ATM038</t>
+          <t>ATM030</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.)</t>
+          <t>BOBAJOY MEYVE SUYU TOPLARI YEŞİL ELMA 4KG KL/4AD (2.)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -8651,73 +10879,185 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ATM030</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>BOBAJOY MEYVE SUYU TOPLARI YEŞİL ELMA 4KG KL/4AD (2.)</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>1-AD</t>
-        </is>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>1980</v>
+      <c r="A17" s="15" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>A00000000259115</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="n">
+        <v>46353</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>1848</v>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
+        <is>
+          <t>Teslim fişi: INTECH SALAMIS KIOSK ŞUBESİ</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
+          <t>ATM070</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2-AD</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>A00000000259190</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>FATURAMIZ</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="n">
+        <v>46356</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>13285</v>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>Teslim fişi: INTECH SALAMIS KIOSK ŞUBESİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ATM017</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ATM038</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ATM030</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI YEŞİL ELMA 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1-AD</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
           <t>ATM040</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>BOBAJOY MEYVE SUYU TOPLARI MANGO 4KG KL/4AD</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>1-AD</t>
         </is>
       </c>
-      <c r="E18" s="1" t="n">
+      <c r="E23" s="1" t="n">
         <v>1980</v>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
+    <row r="24">
+      <c r="B24" t="inlineStr">
         <is>
           <t>PTS032</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>BİO PİPET BEYAZ 6X23 SARGILI PK/200AD KL/25</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>25-PK</t>
         </is>
       </c>
-      <c r="E19" s="1" t="n">
+      <c r="E24" s="1" t="n">
         <v>5365</v>
       </c>
     </row>
-    <row r="21">
-      <c r="C21" s="9" t="inlineStr">
+    <row r="26">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>TOPLAM (net)</t>
         </is>
       </c>
-      <c r="E21" s="10">
-        <f>E4+E7+E12+E14</f>
+      <c r="E26" s="10">
+        <f>E4+E7+E9+E12+E17+E19</f>
         <v/>
       </c>
     </row>
@@ -8726,13 +11066,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8789,618 +11129,2185 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="n">
+      <c r="A4" s="18" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>I00000000246861</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>IADE FATURANIZ</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>-916.49</v>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>GUSSE MEY.PÜRE 1,1LT  YABAN MERSİNİ x1</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="n"/>
+      <c r="G4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>I00000000255472</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>IADE FATURANIZ</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>-12539.6</v>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>BİO PİPET BEYAZ 7X22  PK/250AD KL/20 PK x40</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="n"/>
+      <c r="G5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>TOPLAM (net)</t>
+        </is>
+      </c>
+      <c r="D7" s="1">
+        <f>SUM(D4:D5)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F80"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Şube bazında fatura içerikleri (tutarsız)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>MAĞUSA ŞUBE</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="n"/>
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Tarih</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Fatura No</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Ürün Kodu</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="n">
         <v>46050</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>A00000000242321</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>FATURAMIZ</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>3960</v>
-      </c>
-      <c r="E4" s="17" t="inlineStr">
-        <is>
-          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.) x1; BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.) x1</t>
-        </is>
-      </c>
-      <c r="F4" s="18" t="n"/>
-      <c r="G4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="16" t="n">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ATM038</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="n">
         <v>46050</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>A00000000242321</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ATM017</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>A00000000242322</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>FATURAMIZ</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>1980</v>
-      </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>BOBAJOY MEYVE SUYU TOPLARI FRAMBUAZ 4 KG KL/4AD x1</t>
-        </is>
-      </c>
-      <c r="F5" s="18" t="n"/>
-      <c r="G5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="16" t="n">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ATM041</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI FRAMBUAZ 4 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="n">
         <v>46051</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>A00000000242346</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>FATURAMIZ</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>870</v>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>TEAJOY KONT.BAZ PLASTİK POMPASI x5</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="n"/>
-      <c r="G6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ATM076</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TEAJOY KONT.BAZ PLASTİK POMPASI</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="n">
         <v>46055</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>A00000000242518</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>FATURAMIZ</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>1190.25</v>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>PİPET KAĞIT BYZ BUBBLE 12X24 PK/75AD KL/14PK x10</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="n"/>
-      <c r="G7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>FG004</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PİPET KAĞIT BYZ BUBBLE 12X24 PK/75AD KL/14PK</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="n">
         <v>46056</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>A00000000242620</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>FATURAMIZ</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>11550</v>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>GUA İKİLİ TAŞIYICI PK/100 ADETLİ x1000</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="n"/>
-      <c r="G8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="16" t="n">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MRS0011</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>GUA İKİLİ TAŞIYICI PK/100 ADETLİ</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="n">
         <v>46063</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>A00000000243183</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>FATURAMIZ</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>1291.13</v>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>TEAJOY KONT.BAZ PLASTİK POMPASI x4; PİPET KAĞIT BYZ BUBBLE 12X24 PK/75AD KL/14PK x5</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="n"/>
-      <c r="G9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ATM076</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TEAJOY KONT.BAZ PLASTİK POMPASI</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>A00000000243183</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>FG004</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PİPET KAĞIT BYZ BUBBLE 12X24 PK/75AD KL/14PK</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="n">
         <v>46078</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>A00000000244577</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>FATURAMIZ</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>33852</v>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>GUA RAMAZAN 14 OZ DW KARTON BARDAK KL/500AD x10000</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="n"/>
-      <c r="G10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="16" t="n">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BBT0302</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>GUA RAMAZAN 14 OZ DW KARTON BARDAK KL/500AD</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="n">
         <v>46106</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>A00000000246358</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>FATURAMIZ</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>6153.59</v>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>GUSSE MEY.PÜRE 1,1LT  YABAN MERSİNİ x1; BOBAJOY MEYVE SUYU TOPLARI YEŞİL ELMA 4KG KL/4AD (2.) x1; BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.) x1</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="n"/>
-      <c r="G11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="16" t="n">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>GUS124</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>GUSSE MEY.PÜRE 1,1LT  YABAN MERSİNİ</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>A00000000246358</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ATM030</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI YEŞİL ELMA 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>A00000000246358</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ATM038</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="n">
         <v>46108</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>A00000000246493</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>FATURAMIZ</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>5509.88</v>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>GUA BASKILI 22X11X28 KRAFT DÜZ SAP KL/300 x250; GUSSE MEY.PÜRE 1,1LT  BÖĞÜRTLEN x1</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="n"/>
-      <c r="G12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="16" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MRS0010</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>GUA BASKILI 22X11X28 KRAFT DÜZ SAP KL/300</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="n">
         <v>46108</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>A00000000246493</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>GUS123</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>GUSSE MEY.PÜRE 1,1LT  BÖĞÜRTLEN</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>A00000000246753</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>FATURAMIZ</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>4158</v>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>GUSSE MEY.PÜRE 1,1LT  BÖĞÜRTLEN x6</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="n"/>
-      <c r="G13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="16" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>I00000000246861</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>IADE FATURANIZ</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>-916.49</v>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>GUSSE MEY.PÜRE 1,1LT  YABAN MERSİNİ x1</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="n"/>
-      <c r="G14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="n">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>GUS123</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>GUSSE MEY.PÜRE 1,1LT  BÖĞÜRTLEN</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="n">
         <v>46125</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>A00000000248046</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>FATURAMIZ</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>8118</v>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>GUSSE MEY.PÜRE 1,1LT  BÖĞÜRTLEN x6; BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.) x1; BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.) x1</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="n"/>
-      <c r="G15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="16" t="n">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>GUS123</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>GUSSE MEY.PÜRE 1,1LT  BÖĞÜRTLEN</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>A00000000248046</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ATM017</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>A00000000248046</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ATM038</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="n">
         <v>46141</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>A00000000249366</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>FATURAMIZ</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>7920</v>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>BOBAJOY TOPLARI MANGO 4KG KL/4AD (2.) x1; BOBAJOY MEYVE SUYU TOPLARI YEŞİL ELMA 4KG KL/4AD (2.) x1; BOBAJOY TOPLARI KARAMEL 4 KG KL/4AD (3.) x1; TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD x2</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="n"/>
-      <c r="G16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="16" t="n">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ATM027</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>BOBAJOY TOPLARI MANGO 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>A00000000249366</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ATM030</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI YEŞİL ELMA 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>A00000000249366</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ATM033</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>BOBAJOY TOPLARI KARAMEL 4 KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>A00000000249366</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ATM070</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="n">
         <v>46150</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>A00000000250156</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>FATURAMIZ</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>3960</v>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.) x2</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="n"/>
-      <c r="G17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="16" t="n">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ATM038</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="n">
         <v>46157</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>A00000000250895</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>FATURAMIZ</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>5780.25</v>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>GUA BASKILI 22X11X28 KRAFT DÜZ SAP KL/300 x300</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="n"/>
-      <c r="G18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="16" t="n">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>MRS0010</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>GUA BASKILI 22X11X28 KRAFT DÜZ SAP KL/300</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>300</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="n">
         <v>46162</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>A00000000251139</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>FATURAMIZ</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>8910</v>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>BOBAJOY TOPLARI KARAMEL 4 KG KL/4AD (3.) x1; BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.) x1; BOBAJOY TOPLARI MANGO 4KG KL/4AD (2.) x1; TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD x1; BOBAJOY MEYVE SUYU TOPLARI FRAMBUAZ 4 KG KL/4AD x1</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="n"/>
-      <c r="G19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="16" t="n">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ATM033</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>BOBAJOY TOPLARI KARAMEL 4 KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="n">
         <v>46162</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>A00000000251139</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ATM017</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>A00000000251139</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ATM027</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>BOBAJOY TOPLARI MANGO 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>A00000000251139</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ATM070</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="18" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>A00000000251139</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ATM041</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI FRAMBUAZ 4 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>A00000000252956</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ATM038</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="18" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>A00000000253718</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ATM017</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>A00000000253718</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ATM033</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>BOBAJOY TOPLARI KARAMEL 4 KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="18" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>A00000000253718</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ATM038</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>A00000000253718</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ATM027</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>BOBAJOY TOPLARI MANGO 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="18" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>A00000000253718</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ATM070</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>A00000000254821</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ATM030</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI YEŞİL ELMA 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="18" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>A00000000254821</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ATM027</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>BOBAJOY TOPLARI MANGO 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="18" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>A00000000254821</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ATM038</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="18" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>A00000000254821</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ATM070</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="18" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>A00000000254821</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>PTS030</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>BİO PİPET BEYAZ 7X22  PK/250AD KL/20 PK</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="18" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>A00000000254951</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>PTS038</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>BİO PİPET BEYAZ 8X24 SARGILI PK/250AD KL/20</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="18" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>A00000000255781</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>MRS0010</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>GUA BASKILI 22X11X28 KRAFT DÜZ SAP KL/300</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="n">
+        <v>600</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="18" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>A00000000255781</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ATM017</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="18" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>A00000000255781</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ATM033</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>BOBAJOY TOPLARI KARAMEL 4 KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="18" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>A00000000255781</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ATM070</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="18" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>A00000000255781</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ATM074</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>TEAJOY MR.ORGO (MANGO&amp;PRTKL) 2,5 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="E50" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="18" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>A00000000255791</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ATM057</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI Y.MERSİNİ 1KG KL/12AD</t>
+        </is>
+      </c>
+      <c r="E51" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="18" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>A00000000256524</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CK001</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>PİPET KAĞIT BEYAZ 12X21 SARGILI PK/200AD KL/10PK</t>
+        </is>
+      </c>
+      <c r="E52" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="18" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>A00000000257723</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ATM033</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>BOBAJOY TOPLARI KARAMEL 4 KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="18" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>A00000000257723</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ATM017</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="E54" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="18" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>A00000000259123</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ATM038</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="18" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>A00000000259123</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ATM040</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI MANGO 4KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="18" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>A00000000259123</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>PTS038</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>BİO PİPET BEYAZ 8X24 SARGILI PK/250AD KL/20</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="18" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>A00000000259123</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ATM074</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>TEAJOY MR.ORGO (MANGO&amp;PRTKL) 2,5 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="E58" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>A00000000263425</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ATM033</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>BOBAJOY TOPLARI KARAMEL 4 KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="E59" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>A00000000263425</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>BBT028</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>14 OZ BEYAZ DÜZ KAPAK KL/1000</t>
+        </is>
+      </c>
+      <c r="E60" s="12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="18" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>A00000000263729</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>GUS295</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>GUSTEA DEMLİK SİYAH ÇAY 12 KG</t>
+        </is>
+      </c>
+      <c r="E61" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>INTECH SALAMIS KIOSK</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="n"/>
+      <c r="C64" s="11" t="n"/>
+      <c r="D64" s="11" t="n"/>
+      <c r="E64" s="11" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>Tarih</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>Fatura No</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>Ürün Kodu</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="18" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B66" t="inlineStr">
         <is>
           <t>A00000000251140</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>FATURAMIZ</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>1980</v>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>TEAJOY MR.ORGO (MANGO&amp;PRTKL) 2,5 KG KL/4AD x1; TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD x1</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="n"/>
-      <c r="G20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="16" t="n">
-        <v>46185</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>A00000000252956</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>FATURAMIZ</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>1980</v>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.) x1</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="n"/>
-      <c r="G21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="16" t="n">
-        <v>46196</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>A00000000253718</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>FATURAMIZ</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>9900</v>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.) x1; BOBAJOY TOPLARI KARAMEL 4 KG KL/4AD (3.) x1; BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.) x1; BOBAJOY TOPLARI MANGO 4KG KL/4AD (2.) x1; TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD x2</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="n"/>
-      <c r="G22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="16" t="n">
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ATM074</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>TEAJOY MR.ORGO (MANGO&amp;PRTKL) 2,5 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="E66" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="18" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>A00000000251140</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ATM070</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="E67" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="18" t="n">
         <v>46199</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>A00000000254148</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>FATURAMIZ</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>1980</v>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD x2</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="n"/>
-      <c r="G23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="16" t="n">
-        <v>46207</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>A00000000254821</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>FATURAMIZ</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>19469.6</v>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>BOBAJOY MEYVE SUYU TOPLARI YEŞİL ELMA 4KG KL/4AD (2.) x1; BOBAJOY TOPLARI MANGO 4KG KL/4AD (2.) x1; BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.) x1; TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD x1; BİO PİPET BEYAZ 7X22  PK/250AD KL/20 PK x40</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="n"/>
-      <c r="G24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="16" t="n">
-        <v>46210</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>A00000000254951</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>FATURAMIZ</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>12992</v>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>BİO PİPET BEYAZ 8X24 SARGILI PK/250AD KL/20 x40</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="n"/>
-      <c r="G25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="16" t="n">
-        <v>46217</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>I00000000255472</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>IADE FATURANIZ</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>-12539.6</v>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>BİO PİPET BEYAZ 7X22  PK/250AD KL/20 PK x40</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="n"/>
-      <c r="G26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="16" t="n">
-        <v>46245</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>A00000000257723</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>FATURAMIZ</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>5940</v>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>BOBAJOY TOPLARI KARAMEL 4 KG KL/4AD (3.) x2; BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.) x1</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="n"/>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Fiş var ama 'Teslim Şubesi' boş bırakılmış</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>TOPLAM (net)</t>
-        </is>
-      </c>
-      <c r="D29" s="1">
-        <f>SUM(D4:D27)</f>
-        <v/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ATM070</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="E68" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="18" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>A00000000257286</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ATM074</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>TEAJOY MR.ORGO (MANGO&amp;PRTKL) 2,5 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="18" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>A00000000257286</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ATM070</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="E70" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="18" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>A00000000259067</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ATM017</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="18" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>A00000000259067</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ATM040</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI MANGO 4KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="E72" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="18" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>A00000000259067</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ATM038</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="18" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>A00000000259067</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ATM030</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI YEŞİL ELMA 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="E74" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="18" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>A00000000259115</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ATM070</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>TEAJOY HYPE &amp; JOY (HİBİSKUS) 2,5 KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="18" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>A00000000259190</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ATM017</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE TOPLARI ÇİLEK 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="E76" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="18" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>A00000000259190</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ATM038</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU Y.MERSİNİ 4KG KL/4AD (3.)</t>
+        </is>
+      </c>
+      <c r="E77" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="18" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>A00000000259190</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ATM030</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI YEŞİL ELMA 4KG KL/4AD (2.)</t>
+        </is>
+      </c>
+      <c r="E78" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="18" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>A00000000259190</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ATM040</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>BOBAJOY MEYVE SUYU TOPLARI MANGO 4KG KL/4AD</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="18" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>A00000000259190</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>PTS032</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>BİO PİPET BEYAZ 6X23 SARGILI PK/200AD KL/25</t>
+        </is>
+      </c>
+      <c r="E80" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
       </c>
     </row>
   </sheetData>
